--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,4665 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127295133</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>377237</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6744276</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127295154</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>377487</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6744422</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127295156</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>377489</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6744396</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127295130</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>377203</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6744197</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127295161</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>377576</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6744414</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127295119</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>377599</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6744109</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127295145</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>377331</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6744278</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127295150</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>377507</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6744400</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127295163</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>377441</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6744357</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127295147</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>377575</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6744364</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127295136</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>377216</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6744274</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127295101</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>377493</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6744550</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127295114</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>377455</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6744199</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127295144</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>377285</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6744289</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>127295117</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>377588</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6743996</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>127295134</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79035</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>377206</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6744255</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>127295152</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78769</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>377487</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6744422</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127295112</v>
+      </c>
+      <c r="B20" t="n">
+        <v>78769</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>377452</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6744197</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127295113</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>377452</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6744197</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127295126</v>
+      </c>
+      <c r="B22" t="n">
+        <v>96689</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>53</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>377213</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6744163</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127295106</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>377535</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6744318</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127295162</v>
+      </c>
+      <c r="B24" t="n">
+        <v>78678</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>353</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>377576</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6744414</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>127295160</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>377463</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6744378</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>127295140</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>377379</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6744330</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>127295118</v>
+      </c>
+      <c r="B27" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>377523</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6744132</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>127295115</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>377494</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6744143</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127295164</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>185</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>377671</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6744350</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127295138</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>185</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>377211</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6744196</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127295116</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79600</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>377494</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6744143</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127295105</v>
+      </c>
+      <c r="B32" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>377468</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6744527</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127295100</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78769</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>377499</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6744545</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127295158</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>377488</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6744404</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127295165</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>377640</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6744349</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127295109</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>377479</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6744536</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127295151</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>377506</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6744399</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127295108</v>
+      </c>
+      <c r="B38" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>377545</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6744314</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127295129</v>
+      </c>
+      <c r="B39" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>377236</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6744248</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>127295128</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79043</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>185</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>377209</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6744182</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>127295142</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>377328</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6744286</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>127295107</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>377557</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6744301</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127295135</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>377206</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6744255</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>127295104</v>
+      </c>
+      <c r="B44" t="n">
+        <v>78770</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>377491</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6744551</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>127295155</v>
+      </c>
+      <c r="B45" t="n">
+        <v>78769</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>377489</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6744396</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>127295132</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>377208</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6744241</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>127295121</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>377523</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6744136</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>127295111</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79011</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>377466</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6744500</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>127295167</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79629</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>377647</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6744358</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>127295143</v>
+      </c>
+      <c r="B50" t="n">
+        <v>78678</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>353</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Dvärgbägarlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Cladonia parasitica</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>377379</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6744326</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295133</v>
+        <v>127295154</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377237</v>
+        <v>377487</v>
       </c>
       <c r="R3" t="n">
-        <v>6744276</v>
+        <v>6744422</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +866,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295154</v>
+        <v>127295133</v>
       </c>
       <c r="B4" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377487</v>
+        <v>377237</v>
       </c>
       <c r="R4" t="n">
-        <v>6744422</v>
+        <v>6744276</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R5" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R6" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1179,7 @@
         <v>127295161</v>
       </c>
       <c r="B7" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,7 +1276,7 @@
         <v>127295119</v>
       </c>
       <c r="B8" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>127295145</v>
       </c>
       <c r="B9" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>127295150</v>
       </c>
       <c r="B10" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>127295163</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1664,7 +1664,7 @@
         <v>127295147</v>
       </c>
       <c r="B12" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127295136</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>127295101</v>
       </c>
       <c r="B14" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>127295114</v>
       </c>
       <c r="B15" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>127295144</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>127295117</v>
       </c>
       <c r="B17" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>127295134</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>127295152</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B21" t="n">
-        <v>78770</v>
+        <v>78772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295126</v>
+        <v>127295106</v>
       </c>
       <c r="B22" t="n">
-        <v>96689</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377213</v>
+        <v>377535</v>
       </c>
       <c r="R22" t="n">
-        <v>6744163</v>
+        <v>6744318</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295106</v>
+        <v>127295160</v>
       </c>
       <c r="B23" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377535</v>
+        <v>377463</v>
       </c>
       <c r="R23" t="n">
-        <v>6744318</v>
+        <v>6744378</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295162</v>
+        <v>127295140</v>
       </c>
       <c r="B24" t="n">
-        <v>78678</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377576</v>
+        <v>377379</v>
       </c>
       <c r="R24" t="n">
-        <v>6744414</v>
+        <v>6744330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295160</v>
+        <v>127295126</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>96695</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377463</v>
+        <v>377213</v>
       </c>
       <c r="R25" t="n">
-        <v>6744378</v>
+        <v>6744163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295140</v>
+        <v>127295162</v>
       </c>
       <c r="B26" t="n">
-        <v>79011</v>
+        <v>78681</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377379</v>
+        <v>377576</v>
       </c>
       <c r="R26" t="n">
-        <v>6744330</v>
+        <v>6744414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295118</v>
+        <v>127295115</v>
       </c>
       <c r="B27" t="n">
-        <v>78770</v>
+        <v>79632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377523</v>
+        <v>377494</v>
       </c>
       <c r="R27" t="n">
-        <v>6744132</v>
+        <v>6744143</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295115</v>
+        <v>127295164</v>
       </c>
       <c r="B28" t="n">
-        <v>79629</v>
+        <v>79046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377494</v>
+        <v>377671</v>
       </c>
       <c r="R28" t="n">
-        <v>6744143</v>
+        <v>6744350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295164</v>
+        <v>127295118</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377671</v>
+        <v>377523</v>
       </c>
       <c r="R29" t="n">
-        <v>6744350</v>
+        <v>6744132</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
         <v>127295138</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>127295116</v>
       </c>
       <c r="B31" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>127295105</v>
       </c>
       <c r="B32" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>127295100</v>
       </c>
       <c r="B33" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>127295158</v>
       </c>
       <c r="B34" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>127295165</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>127295109</v>
       </c>
       <c r="B36" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>127295151</v>
       </c>
       <c r="B37" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>127295108</v>
       </c>
       <c r="B38" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>127295129</v>
       </c>
       <c r="B39" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>127295128</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79046</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295142</v>
+        <v>127295107</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377328</v>
+        <v>377557</v>
       </c>
       <c r="R41" t="n">
-        <v>6744286</v>
+        <v>6744301</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295107</v>
+        <v>127295142</v>
       </c>
       <c r="B42" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4583,21 +4583,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>377557</v>
+        <v>377328</v>
       </c>
       <c r="R42" t="n">
-        <v>6744301</v>
+        <v>6744286</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
         <v>127295135</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B44" t="n">
-        <v>78770</v>
+        <v>78772</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R44" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B45" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R45" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,7 +4963,7 @@
         <v>127295132</v>
       </c>
       <c r="B46" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>127295121</v>
       </c>
       <c r="B47" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>127295111</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>127295167</v>
       </c>
       <c r="B49" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,7 +5352,7 @@
         <v>127295143</v>
       </c>
       <c r="B50" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R5" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R6" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295145</v>
+        <v>127295150</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377331</v>
+        <v>377507</v>
       </c>
       <c r="R9" t="n">
-        <v>6744278</v>
+        <v>6744400</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295150</v>
+        <v>127295163</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377507</v>
+        <v>377441</v>
       </c>
       <c r="R10" t="n">
-        <v>6744400</v>
+        <v>6744357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295163</v>
+        <v>127295145</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377441</v>
+        <v>377331</v>
       </c>
       <c r="R11" t="n">
-        <v>6744357</v>
+        <v>6744278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295136</v>
+        <v>127295101</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377216</v>
+        <v>377493</v>
       </c>
       <c r="R13" t="n">
-        <v>6744274</v>
+        <v>6744550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295101</v>
+        <v>127295114</v>
       </c>
       <c r="B14" t="n">
         <v>79632</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377493</v>
+        <v>377455</v>
       </c>
       <c r="R14" t="n">
-        <v>6744550</v>
+        <v>6744199</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295114</v>
+        <v>127295136</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377455</v>
+        <v>377216</v>
       </c>
       <c r="R15" t="n">
-        <v>6744199</v>
+        <v>6744274</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295160</v>
+        <v>127295126</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>96695</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377463</v>
+        <v>377213</v>
       </c>
       <c r="R23" t="n">
-        <v>6744378</v>
+        <v>6744163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295140</v>
+        <v>127295162</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377379</v>
+        <v>377576</v>
       </c>
       <c r="R24" t="n">
-        <v>6744330</v>
+        <v>6744414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295126</v>
+        <v>127295160</v>
       </c>
       <c r="B25" t="n">
-        <v>96695</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377213</v>
+        <v>377463</v>
       </c>
       <c r="R25" t="n">
-        <v>6744163</v>
+        <v>6744378</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295162</v>
+        <v>127295140</v>
       </c>
       <c r="B26" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377576</v>
+        <v>377379</v>
       </c>
       <c r="R26" t="n">
-        <v>6744414</v>
+        <v>6744330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295115</v>
+        <v>127295164</v>
       </c>
       <c r="B27" t="n">
-        <v>79632</v>
+        <v>79046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377494</v>
+        <v>377671</v>
       </c>
       <c r="R27" t="n">
-        <v>6744143</v>
+        <v>6744350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295164</v>
+        <v>127295118</v>
       </c>
       <c r="B28" t="n">
-        <v>79046</v>
+        <v>78773</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377671</v>
+        <v>377523</v>
       </c>
       <c r="R28" t="n">
-        <v>6744350</v>
+        <v>6744132</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295118</v>
+        <v>127295115</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377523</v>
+        <v>377494</v>
       </c>
       <c r="R29" t="n">
-        <v>6744132</v>
+        <v>6744143</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295116</v>
+        <v>127295100</v>
       </c>
       <c r="B31" t="n">
-        <v>79603</v>
+        <v>78772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377494</v>
+        <v>377499</v>
       </c>
       <c r="R31" t="n">
-        <v>6744143</v>
+        <v>6744545</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295105</v>
+        <v>127295158</v>
       </c>
       <c r="B32" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377468</v>
+        <v>377488</v>
       </c>
       <c r="R32" t="n">
-        <v>6744527</v>
+        <v>6744404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295100</v>
+        <v>127295165</v>
       </c>
       <c r="B33" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377499</v>
+        <v>377640</v>
       </c>
       <c r="R33" t="n">
-        <v>6744545</v>
+        <v>6744349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295158</v>
+        <v>127295105</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377488</v>
+        <v>377468</v>
       </c>
       <c r="R34" t="n">
-        <v>6744404</v>
+        <v>6744527</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295165</v>
+        <v>127295116</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377640</v>
+        <v>377494</v>
       </c>
       <c r="R35" t="n">
-        <v>6744349</v>
+        <v>6744143</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B39" t="n">
-        <v>78773</v>
+        <v>79046</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R39" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B40" t="n">
-        <v>79046</v>
+        <v>78773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R40" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295107</v>
+        <v>127295142</v>
       </c>
       <c r="B41" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377557</v>
+        <v>377328</v>
       </c>
       <c r="R41" t="n">
-        <v>6744301</v>
+        <v>6744286</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295142</v>
+        <v>127295135</v>
       </c>
       <c r="B42" t="n">
         <v>79014</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>377328</v>
+        <v>377206</v>
       </c>
       <c r="R42" t="n">
-        <v>6744286</v>
+        <v>6744255</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295135</v>
+        <v>127295107</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>377206</v>
+        <v>377557</v>
       </c>
       <c r="R43" t="n">
-        <v>6744255</v>
+        <v>6744301</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295111</v>
+        <v>127295143</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377466</v>
+        <v>377379</v>
       </c>
       <c r="R48" t="n">
-        <v>6744500</v>
+        <v>6744326</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,10 +5349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295143</v>
+        <v>127295111</v>
       </c>
       <c r="B50" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377379</v>
+        <v>377466</v>
       </c>
       <c r="R50" t="n">
-        <v>6744326</v>
+        <v>6744500</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295117</v>
+        <v>127295134</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>377588</v>
+        <v>377206</v>
       </c>
       <c r="R17" t="n">
-        <v>6743996</v>
+        <v>6744255</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295134</v>
+        <v>127295117</v>
       </c>
       <c r="B18" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377206</v>
+        <v>377588</v>
       </c>
       <c r="R18" t="n">
-        <v>6744255</v>
+        <v>6743996</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295106</v>
+        <v>127295126</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>96695</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377535</v>
+        <v>377213</v>
       </c>
       <c r="R22" t="n">
-        <v>6744318</v>
+        <v>6744163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295126</v>
+        <v>127295162</v>
       </c>
       <c r="B23" t="n">
-        <v>96695</v>
+        <v>78681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377213</v>
+        <v>377576</v>
       </c>
       <c r="R23" t="n">
-        <v>6744163</v>
+        <v>6744414</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295162</v>
+        <v>127295160</v>
       </c>
       <c r="B24" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377576</v>
+        <v>377463</v>
       </c>
       <c r="R24" t="n">
-        <v>6744414</v>
+        <v>6744378</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295160</v>
+        <v>127295140</v>
       </c>
       <c r="B25" t="n">
         <v>79014</v>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377463</v>
+        <v>377379</v>
       </c>
       <c r="R25" t="n">
-        <v>6744378</v>
+        <v>6744330</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295140</v>
+        <v>127295106</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377379</v>
+        <v>377535</v>
       </c>
       <c r="R26" t="n">
-        <v>6744330</v>
+        <v>6744318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295142</v>
+        <v>127295107</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377328</v>
+        <v>377557</v>
       </c>
       <c r="R41" t="n">
-        <v>6744286</v>
+        <v>6744301</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295135</v>
+        <v>127295142</v>
       </c>
       <c r="B42" t="n">
         <v>79014</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>377206</v>
+        <v>377328</v>
       </c>
       <c r="R42" t="n">
-        <v>6744255</v>
+        <v>6744286</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295107</v>
+        <v>127295135</v>
       </c>
       <c r="B43" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>377557</v>
+        <v>377206</v>
       </c>
       <c r="R43" t="n">
-        <v>6744301</v>
+        <v>6744255</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295154</v>
+        <v>127295133</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377487</v>
+        <v>377237</v>
       </c>
       <c r="R3" t="n">
-        <v>6744422</v>
+        <v>6744276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295133</v>
+        <v>127295154</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377237</v>
+        <v>377487</v>
       </c>
       <c r="R4" t="n">
-        <v>6744276</v>
+        <v>6744422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R5" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R6" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295150</v>
+        <v>127295145</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377507</v>
+        <v>377331</v>
       </c>
       <c r="R9" t="n">
-        <v>6744400</v>
+        <v>6744278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295163</v>
+        <v>127295150</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377441</v>
+        <v>377507</v>
       </c>
       <c r="R10" t="n">
-        <v>6744357</v>
+        <v>6744400</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,7 +1564,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295145</v>
+        <v>127295163</v>
       </c>
       <c r="B11" t="n">
         <v>79014</v>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377331</v>
+        <v>377441</v>
       </c>
       <c r="R11" t="n">
-        <v>6744278</v>
+        <v>6744357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295147</v>
+        <v>127295136</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377575</v>
+        <v>377216</v>
       </c>
       <c r="R12" t="n">
-        <v>6744364</v>
+        <v>6744274</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295101</v>
+        <v>127295147</v>
       </c>
       <c r="B13" t="n">
         <v>79632</v>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377493</v>
+        <v>377575</v>
       </c>
       <c r="R13" t="n">
-        <v>6744550</v>
+        <v>6744364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295114</v>
+        <v>127295101</v>
       </c>
       <c r="B14" t="n">
         <v>79632</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377455</v>
+        <v>377493</v>
       </c>
       <c r="R14" t="n">
-        <v>6744199</v>
+        <v>6744550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295136</v>
+        <v>127295114</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377216</v>
+        <v>377455</v>
       </c>
       <c r="R15" t="n">
-        <v>6744274</v>
+        <v>6744199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295134</v>
+        <v>127295117</v>
       </c>
       <c r="B17" t="n">
-        <v>79038</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>377206</v>
+        <v>377588</v>
       </c>
       <c r="R17" t="n">
-        <v>6744255</v>
+        <v>6743996</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295117</v>
+        <v>127295134</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>79038</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377588</v>
+        <v>377206</v>
       </c>
       <c r="R18" t="n">
-        <v>6743996</v>
+        <v>6744255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B21" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295126</v>
+        <v>127295160</v>
       </c>
       <c r="B22" t="n">
-        <v>96695</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377213</v>
+        <v>377463</v>
       </c>
       <c r="R22" t="n">
-        <v>6744163</v>
+        <v>6744378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295162</v>
+        <v>127295126</v>
       </c>
       <c r="B23" t="n">
-        <v>78681</v>
+        <v>96696</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377576</v>
+        <v>377213</v>
       </c>
       <c r="R23" t="n">
-        <v>6744414</v>
+        <v>6744163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295160</v>
+        <v>127295162</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377463</v>
+        <v>377576</v>
       </c>
       <c r="R24" t="n">
-        <v>6744378</v>
+        <v>6744414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295164</v>
+        <v>127295115</v>
       </c>
       <c r="B27" t="n">
-        <v>79046</v>
+        <v>79632</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377671</v>
+        <v>377494</v>
       </c>
       <c r="R27" t="n">
-        <v>6744350</v>
+        <v>6744143</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295118</v>
+        <v>127295164</v>
       </c>
       <c r="B28" t="n">
-        <v>78773</v>
+        <v>79046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377523</v>
+        <v>377671</v>
       </c>
       <c r="R28" t="n">
-        <v>6744132</v>
+        <v>6744350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295115</v>
+        <v>127295118</v>
       </c>
       <c r="B29" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377494</v>
+        <v>377523</v>
       </c>
       <c r="R29" t="n">
-        <v>6744143</v>
+        <v>6744132</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295138</v>
+        <v>127295116</v>
       </c>
       <c r="B30" t="n">
-        <v>79046</v>
+        <v>79603</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377211</v>
+        <v>377494</v>
       </c>
       <c r="R30" t="n">
-        <v>6744196</v>
+        <v>6744143</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295100</v>
+        <v>127295105</v>
       </c>
       <c r="B31" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377499</v>
+        <v>377468</v>
       </c>
       <c r="R31" t="n">
-        <v>6744545</v>
+        <v>6744527</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295158</v>
+        <v>127295138</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377488</v>
+        <v>377211</v>
       </c>
       <c r="R32" t="n">
-        <v>6744404</v>
+        <v>6744196</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295165</v>
+        <v>127295100</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377640</v>
+        <v>377499</v>
       </c>
       <c r="R33" t="n">
-        <v>6744349</v>
+        <v>6744545</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295105</v>
+        <v>127295158</v>
       </c>
       <c r="B34" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377468</v>
+        <v>377488</v>
       </c>
       <c r="R34" t="n">
-        <v>6744527</v>
+        <v>6744404</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295116</v>
+        <v>127295165</v>
       </c>
       <c r="B35" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377494</v>
+        <v>377640</v>
       </c>
       <c r="R35" t="n">
-        <v>6744143</v>
+        <v>6744349</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B39" t="n">
-        <v>79046</v>
+        <v>78773</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R39" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B40" t="n">
-        <v>78773</v>
+        <v>79046</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R40" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295107</v>
+        <v>127295142</v>
       </c>
       <c r="B41" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377557</v>
+        <v>377328</v>
       </c>
       <c r="R41" t="n">
-        <v>6744301</v>
+        <v>6744286</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295142</v>
+        <v>127295135</v>
       </c>
       <c r="B42" t="n">
         <v>79014</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>377328</v>
+        <v>377206</v>
       </c>
       <c r="R42" t="n">
-        <v>6744286</v>
+        <v>6744255</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295135</v>
+        <v>127295107</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>377206</v>
+        <v>377557</v>
       </c>
       <c r="R43" t="n">
-        <v>6744255</v>
+        <v>6744301</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295132</v>
+        <v>127295121</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4971,21 +4971,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>377208</v>
+        <v>377523</v>
       </c>
       <c r="R46" t="n">
-        <v>6744241</v>
+        <v>6744136</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295121</v>
+        <v>127295132</v>
       </c>
       <c r="B47" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>377523</v>
+        <v>377208</v>
       </c>
       <c r="R47" t="n">
-        <v>6744136</v>
+        <v>6744241</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R5" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R6" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295161</v>
+        <v>127295119</v>
       </c>
       <c r="B7" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377576</v>
+        <v>377599</v>
       </c>
       <c r="R7" t="n">
-        <v>6744414</v>
+        <v>6744109</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295119</v>
+        <v>127295145</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377599</v>
+        <v>377331</v>
       </c>
       <c r="R8" t="n">
-        <v>6744109</v>
+        <v>6744278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295145</v>
+        <v>127295150</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377331</v>
+        <v>377507</v>
       </c>
       <c r="R9" t="n">
-        <v>6744278</v>
+        <v>6744400</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295150</v>
+        <v>127295163</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377507</v>
+        <v>377441</v>
       </c>
       <c r="R10" t="n">
-        <v>6744400</v>
+        <v>6744357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295163</v>
+        <v>127295161</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377441</v>
+        <v>377576</v>
       </c>
       <c r="R11" t="n">
-        <v>6744357</v>
+        <v>6744414</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295136</v>
+        <v>127295147</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377216</v>
+        <v>377575</v>
       </c>
       <c r="R12" t="n">
-        <v>6744274</v>
+        <v>6744364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295147</v>
+        <v>127295101</v>
       </c>
       <c r="B13" t="n">
         <v>79632</v>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377575</v>
+        <v>377493</v>
       </c>
       <c r="R13" t="n">
-        <v>6744364</v>
+        <v>6744550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295101</v>
+        <v>127295114</v>
       </c>
       <c r="B14" t="n">
         <v>79632</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377493</v>
+        <v>377455</v>
       </c>
       <c r="R14" t="n">
-        <v>6744550</v>
+        <v>6744199</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295114</v>
+        <v>127295136</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377455</v>
+        <v>377216</v>
       </c>
       <c r="R15" t="n">
-        <v>6744199</v>
+        <v>6744274</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295160</v>
+        <v>127295126</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>96696</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377463</v>
+        <v>377213</v>
       </c>
       <c r="R22" t="n">
-        <v>6744378</v>
+        <v>6744163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295126</v>
+        <v>127295162</v>
       </c>
       <c r="B23" t="n">
-        <v>96696</v>
+        <v>78681</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377213</v>
+        <v>377576</v>
       </c>
       <c r="R23" t="n">
-        <v>6744163</v>
+        <v>6744414</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295162</v>
+        <v>127295140</v>
       </c>
       <c r="B24" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377576</v>
+        <v>377379</v>
       </c>
       <c r="R24" t="n">
-        <v>6744414</v>
+        <v>6744330</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295140</v>
+        <v>127295106</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377379</v>
+        <v>377535</v>
       </c>
       <c r="R25" t="n">
-        <v>6744330</v>
+        <v>6744318</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295106</v>
+        <v>127295160</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377535</v>
+        <v>377463</v>
       </c>
       <c r="R26" t="n">
-        <v>6744318</v>
+        <v>6744378</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295115</v>
+        <v>127295118</v>
       </c>
       <c r="B27" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377494</v>
+        <v>377523</v>
       </c>
       <c r="R27" t="n">
-        <v>6744143</v>
+        <v>6744132</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295118</v>
+        <v>127295115</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377523</v>
+        <v>377494</v>
       </c>
       <c r="R29" t="n">
-        <v>6744132</v>
+        <v>6744143</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295116</v>
+        <v>127295138</v>
       </c>
       <c r="B30" t="n">
-        <v>79603</v>
+        <v>79046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377494</v>
+        <v>377211</v>
       </c>
       <c r="R30" t="n">
-        <v>6744143</v>
+        <v>6744196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295105</v>
+        <v>127295100</v>
       </c>
       <c r="B31" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377468</v>
+        <v>377499</v>
       </c>
       <c r="R31" t="n">
-        <v>6744527</v>
+        <v>6744545</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295138</v>
+        <v>127295158</v>
       </c>
       <c r="B32" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377211</v>
+        <v>377488</v>
       </c>
       <c r="R32" t="n">
-        <v>6744196</v>
+        <v>6744404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295100</v>
+        <v>127295165</v>
       </c>
       <c r="B33" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377499</v>
+        <v>377640</v>
       </c>
       <c r="R33" t="n">
-        <v>6744545</v>
+        <v>6744349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295158</v>
+        <v>127295116</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377488</v>
+        <v>377494</v>
       </c>
       <c r="R34" t="n">
-        <v>6744404</v>
+        <v>6744143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295165</v>
+        <v>127295105</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377640</v>
+        <v>377468</v>
       </c>
       <c r="R35" t="n">
-        <v>6744349</v>
+        <v>6744527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B44" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R44" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B45" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R45" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R5" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R6" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295119</v>
+        <v>127295145</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377599</v>
+        <v>377331</v>
       </c>
       <c r="R7" t="n">
-        <v>6744109</v>
+        <v>6744278</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295145</v>
+        <v>127295163</v>
       </c>
       <c r="B8" t="n">
         <v>79014</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377331</v>
+        <v>377441</v>
       </c>
       <c r="R8" t="n">
-        <v>6744278</v>
+        <v>6744357</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295150</v>
+        <v>127295119</v>
       </c>
       <c r="B9" t="n">
         <v>79632</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377507</v>
+        <v>377599</v>
       </c>
       <c r="R9" t="n">
-        <v>6744400</v>
+        <v>6744109</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295163</v>
+        <v>127295150</v>
       </c>
       <c r="B10" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377441</v>
+        <v>377507</v>
       </c>
       <c r="R10" t="n">
-        <v>6744357</v>
+        <v>6744400</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295147</v>
+        <v>127295136</v>
       </c>
       <c r="B12" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377575</v>
+        <v>377216</v>
       </c>
       <c r="R12" t="n">
-        <v>6744364</v>
+        <v>6744274</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295101</v>
+        <v>127295147</v>
       </c>
       <c r="B13" t="n">
         <v>79632</v>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377493</v>
+        <v>377575</v>
       </c>
       <c r="R13" t="n">
-        <v>6744550</v>
+        <v>6744364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295136</v>
+        <v>127295101</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377216</v>
+        <v>377493</v>
       </c>
       <c r="R15" t="n">
-        <v>6744274</v>
+        <v>6744550</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B21" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295106</v>
+        <v>127295160</v>
       </c>
       <c r="B25" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377535</v>
+        <v>377463</v>
       </c>
       <c r="R25" t="n">
-        <v>6744318</v>
+        <v>6744378</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295160</v>
+        <v>127295106</v>
       </c>
       <c r="B26" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377463</v>
+        <v>377535</v>
       </c>
       <c r="R26" t="n">
-        <v>6744378</v>
+        <v>6744318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295118</v>
+        <v>127295164</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>79046</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377523</v>
+        <v>377671</v>
       </c>
       <c r="R27" t="n">
-        <v>6744132</v>
+        <v>6744350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295164</v>
+        <v>127295115</v>
       </c>
       <c r="B28" t="n">
-        <v>79046</v>
+        <v>79632</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377671</v>
+        <v>377494</v>
       </c>
       <c r="R28" t="n">
-        <v>6744350</v>
+        <v>6744143</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295115</v>
+        <v>127295118</v>
       </c>
       <c r="B29" t="n">
-        <v>79632</v>
+        <v>78773</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377494</v>
+        <v>377523</v>
       </c>
       <c r="R29" t="n">
-        <v>6744143</v>
+        <v>6744132</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295138</v>
+        <v>127295100</v>
       </c>
       <c r="B30" t="n">
-        <v>79046</v>
+        <v>78772</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377211</v>
+        <v>377499</v>
       </c>
       <c r="R30" t="n">
-        <v>6744196</v>
+        <v>6744545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295100</v>
+        <v>127295158</v>
       </c>
       <c r="B31" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377499</v>
+        <v>377488</v>
       </c>
       <c r="R31" t="n">
-        <v>6744545</v>
+        <v>6744404</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295158</v>
+        <v>127295165</v>
       </c>
       <c r="B32" t="n">
         <v>79014</v>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377488</v>
+        <v>377640</v>
       </c>
       <c r="R32" t="n">
-        <v>6744404</v>
+        <v>6744349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295165</v>
+        <v>127295138</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79046</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377640</v>
+        <v>377211</v>
       </c>
       <c r="R33" t="n">
-        <v>6744349</v>
+        <v>6744196</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B39" t="n">
-        <v>78773</v>
+        <v>79046</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R39" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B40" t="n">
-        <v>79046</v>
+        <v>78773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R40" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B44" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R44" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B45" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R45" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295121</v>
+        <v>127295132</v>
       </c>
       <c r="B46" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4971,21 +4971,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>377523</v>
+        <v>377208</v>
       </c>
       <c r="R46" t="n">
-        <v>6744136</v>
+        <v>6744241</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295132</v>
+        <v>127295121</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>377208</v>
+        <v>377523</v>
       </c>
       <c r="R47" t="n">
-        <v>6744241</v>
+        <v>6744136</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295143</v>
+        <v>127295167</v>
       </c>
       <c r="B48" t="n">
-        <v>78681</v>
+        <v>79632</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377379</v>
+        <v>377647</v>
       </c>
       <c r="R48" t="n">
-        <v>6744326</v>
+        <v>6744358</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5233,6 +5233,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5251,10 +5252,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295167</v>
+        <v>127295111</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5262,21 +5263,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5286,10 +5287,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377647</v>
+        <v>377466</v>
       </c>
       <c r="R49" t="n">
-        <v>6744358</v>
+        <v>6744500</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5330,7 +5331,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5349,10 +5349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295111</v>
+        <v>127295143</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>78681</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377466</v>
+        <v>377379</v>
       </c>
       <c r="R50" t="n">
-        <v>6744500</v>
+        <v>6744326</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R5" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R6" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295126</v>
+        <v>127295106</v>
       </c>
       <c r="B22" t="n">
-        <v>96696</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377213</v>
+        <v>377535</v>
       </c>
       <c r="R22" t="n">
-        <v>6744163</v>
+        <v>6744318</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295162</v>
+        <v>127295160</v>
       </c>
       <c r="B23" t="n">
-        <v>78681</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377576</v>
+        <v>377463</v>
       </c>
       <c r="R23" t="n">
-        <v>6744414</v>
+        <v>6744378</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295160</v>
+        <v>127295126</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>96696</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377463</v>
+        <v>377213</v>
       </c>
       <c r="R25" t="n">
-        <v>6744378</v>
+        <v>6744163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295106</v>
+        <v>127295162</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>78681</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377535</v>
+        <v>377576</v>
       </c>
       <c r="R26" t="n">
-        <v>6744318</v>
+        <v>6744414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295109</v>
+        <v>127295151</v>
       </c>
       <c r="B36" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>377479</v>
+        <v>377506</v>
       </c>
       <c r="R36" t="n">
-        <v>6744536</v>
+        <v>6744399</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295151</v>
+        <v>127295108</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>377506</v>
+        <v>377545</v>
       </c>
       <c r="R37" t="n">
-        <v>6744399</v>
+        <v>6744314</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295108</v>
+        <v>127295109</v>
       </c>
       <c r="B38" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>377545</v>
+        <v>377479</v>
       </c>
       <c r="R38" t="n">
-        <v>6744314</v>
+        <v>6744536</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B39" t="n">
-        <v>79046</v>
+        <v>78773</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R39" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B40" t="n">
-        <v>78773</v>
+        <v>79046</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R40" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R5" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R6" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295164</v>
+        <v>127295118</v>
       </c>
       <c r="B27" t="n">
-        <v>79046</v>
+        <v>78773</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377671</v>
+        <v>377523</v>
       </c>
       <c r="R27" t="n">
-        <v>6744350</v>
+        <v>6744132</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295115</v>
+        <v>127295164</v>
       </c>
       <c r="B28" t="n">
-        <v>79632</v>
+        <v>79046</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377494</v>
+        <v>377671</v>
       </c>
       <c r="R28" t="n">
-        <v>6744143</v>
+        <v>6744350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295118</v>
+        <v>127295115</v>
       </c>
       <c r="B29" t="n">
-        <v>78773</v>
+        <v>79632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377523</v>
+        <v>377494</v>
       </c>
       <c r="R29" t="n">
-        <v>6744132</v>
+        <v>6744143</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295100</v>
+        <v>127295138</v>
       </c>
       <c r="B30" t="n">
-        <v>78772</v>
+        <v>79046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377499</v>
+        <v>377211</v>
       </c>
       <c r="R30" t="n">
-        <v>6744545</v>
+        <v>6744196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295158</v>
+        <v>127295100</v>
       </c>
       <c r="B31" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377488</v>
+        <v>377499</v>
       </c>
       <c r="R31" t="n">
-        <v>6744404</v>
+        <v>6744545</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295165</v>
+        <v>127295158</v>
       </c>
       <c r="B32" t="n">
         <v>79014</v>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377640</v>
+        <v>377488</v>
       </c>
       <c r="R32" t="n">
-        <v>6744349</v>
+        <v>6744404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295138</v>
+        <v>127295165</v>
       </c>
       <c r="B33" t="n">
-        <v>79046</v>
+        <v>79014</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377211</v>
+        <v>377640</v>
       </c>
       <c r="R33" t="n">
-        <v>6744196</v>
+        <v>6744349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295167</v>
+        <v>127295111</v>
       </c>
       <c r="B48" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377647</v>
+        <v>377466</v>
       </c>
       <c r="R48" t="n">
-        <v>6744358</v>
+        <v>6744500</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5233,7 +5233,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5252,10 +5251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295111</v>
+        <v>127295167</v>
       </c>
       <c r="B49" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5263,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5287,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377466</v>
+        <v>377647</v>
       </c>
       <c r="R49" t="n">
-        <v>6744500</v>
+        <v>6744358</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5331,6 +5330,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127295133</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127295154</v>
       </c>
       <c r="B4" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295145</v>
+        <v>127295161</v>
       </c>
       <c r="B7" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377331</v>
+        <v>377576</v>
       </c>
       <c r="R7" t="n">
-        <v>6744278</v>
+        <v>6744414</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295163</v>
+        <v>127295119</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377441</v>
+        <v>377599</v>
       </c>
       <c r="R8" t="n">
-        <v>6744357</v>
+        <v>6744109</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295119</v>
+        <v>127295145</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377599</v>
+        <v>377331</v>
       </c>
       <c r="R9" t="n">
-        <v>6744109</v>
+        <v>6744278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
         <v>127295150</v>
       </c>
       <c r="B10" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295161</v>
+        <v>127295163</v>
       </c>
       <c r="B11" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377576</v>
+        <v>377441</v>
       </c>
       <c r="R11" t="n">
-        <v>6744414</v>
+        <v>6744357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295136</v>
+        <v>127295147</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377216</v>
+        <v>377575</v>
       </c>
       <c r="R12" t="n">
-        <v>6744274</v>
+        <v>6744364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295147</v>
+        <v>127295136</v>
       </c>
       <c r="B13" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377575</v>
+        <v>377216</v>
       </c>
       <c r="R13" t="n">
-        <v>6744364</v>
+        <v>6744274</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295114</v>
+        <v>127295101</v>
       </c>
       <c r="B14" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377455</v>
+        <v>377493</v>
       </c>
       <c r="R14" t="n">
-        <v>6744199</v>
+        <v>6744550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295101</v>
+        <v>127295114</v>
       </c>
       <c r="B15" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377493</v>
+        <v>377455</v>
       </c>
       <c r="R15" t="n">
-        <v>6744550</v>
+        <v>6744199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>127295144</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>127295117</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>127295134</v>
       </c>
       <c r="B18" t="n">
-        <v>79038</v>
+        <v>79042</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>127295152</v>
       </c>
       <c r="B19" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295106</v>
+        <v>127295126</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>96700</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377535</v>
+        <v>377213</v>
       </c>
       <c r="R22" t="n">
-        <v>6744318</v>
+        <v>6744163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295160</v>
+        <v>127295162</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377463</v>
+        <v>377576</v>
       </c>
       <c r="R23" t="n">
-        <v>6744378</v>
+        <v>6744414</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295140</v>
+        <v>127295160</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377379</v>
+        <v>377463</v>
       </c>
       <c r="R24" t="n">
-        <v>6744330</v>
+        <v>6744378</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295126</v>
+        <v>127295140</v>
       </c>
       <c r="B25" t="n">
-        <v>96696</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377213</v>
+        <v>377379</v>
       </c>
       <c r="R25" t="n">
-        <v>6744163</v>
+        <v>6744330</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295162</v>
+        <v>127295106</v>
       </c>
       <c r="B26" t="n">
-        <v>78681</v>
+        <v>78777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377576</v>
+        <v>377535</v>
       </c>
       <c r="R26" t="n">
-        <v>6744414</v>
+        <v>6744318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295118</v>
+        <v>127295164</v>
       </c>
       <c r="B27" t="n">
-        <v>78773</v>
+        <v>79050</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377523</v>
+        <v>377671</v>
       </c>
       <c r="R27" t="n">
-        <v>6744132</v>
+        <v>6744350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295164</v>
+        <v>127295115</v>
       </c>
       <c r="B28" t="n">
-        <v>79046</v>
+        <v>79636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377671</v>
+        <v>377494</v>
       </c>
       <c r="R28" t="n">
-        <v>6744350</v>
+        <v>6744143</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295115</v>
+        <v>127295118</v>
       </c>
       <c r="B29" t="n">
-        <v>79632</v>
+        <v>78777</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377494</v>
+        <v>377523</v>
       </c>
       <c r="R29" t="n">
-        <v>6744143</v>
+        <v>6744132</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
         <v>127295138</v>
       </c>
       <c r="B30" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>127295100</v>
       </c>
       <c r="B31" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>127295158</v>
       </c>
       <c r="B32" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>127295165</v>
       </c>
       <c r="B33" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3799,7 +3799,7 @@
         <v>127295116</v>
       </c>
       <c r="B34" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3896,7 +3896,7 @@
         <v>127295105</v>
       </c>
       <c r="B35" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295151</v>
+        <v>127295109</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>377506</v>
+        <v>377479</v>
       </c>
       <c r="R36" t="n">
-        <v>6744399</v>
+        <v>6744536</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295108</v>
+        <v>127295151</v>
       </c>
       <c r="B37" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>377545</v>
+        <v>377506</v>
       </c>
       <c r="R37" t="n">
-        <v>6744314</v>
+        <v>6744399</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295109</v>
+        <v>127295108</v>
       </c>
       <c r="B38" t="n">
-        <v>79632</v>
+        <v>78777</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>377479</v>
+        <v>377545</v>
       </c>
       <c r="R38" t="n">
-        <v>6744536</v>
+        <v>6744314</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4284,7 +4284,7 @@
         <v>127295129</v>
       </c>
       <c r="B39" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>127295128</v>
       </c>
       <c r="B40" t="n">
-        <v>79046</v>
+        <v>79050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>127295142</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>127295135</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>127295107</v>
       </c>
       <c r="B43" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>127295155</v>
       </c>
       <c r="B44" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>127295104</v>
       </c>
       <c r="B45" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>127295132</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>127295121</v>
       </c>
       <c r="B47" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295111</v>
+        <v>127295143</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>78685</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377466</v>
+        <v>377379</v>
       </c>
       <c r="R48" t="n">
-        <v>6744500</v>
+        <v>6744326</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295167</v>
+        <v>127295111</v>
       </c>
       <c r="B49" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377647</v>
+        <v>377466</v>
       </c>
       <c r="R49" t="n">
-        <v>6744358</v>
+        <v>6744500</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5330,7 +5330,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5349,10 +5348,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295143</v>
+        <v>127295167</v>
       </c>
       <c r="B50" t="n">
-        <v>78681</v>
+        <v>79636</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5360,21 +5359,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5384,10 +5383,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377379</v>
+        <v>377647</v>
       </c>
       <c r="R50" t="n">
-        <v>6744326</v>
+        <v>6744358</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5428,6 +5427,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R5" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R6" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295161</v>
+        <v>127295119</v>
       </c>
       <c r="B7" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377576</v>
+        <v>377599</v>
       </c>
       <c r="R7" t="n">
-        <v>6744414</v>
+        <v>6744109</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295119</v>
+        <v>127295150</v>
       </c>
       <c r="B8" t="n">
         <v>79636</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377599</v>
+        <v>377507</v>
       </c>
       <c r="R8" t="n">
-        <v>6744109</v>
+        <v>6744400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295145</v>
+        <v>127295163</v>
       </c>
       <c r="B9" t="n">
         <v>79018</v>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377331</v>
+        <v>377441</v>
       </c>
       <c r="R9" t="n">
-        <v>6744278</v>
+        <v>6744357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295150</v>
+        <v>127295145</v>
       </c>
       <c r="B10" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377507</v>
+        <v>377331</v>
       </c>
       <c r="R10" t="n">
-        <v>6744400</v>
+        <v>6744278</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295163</v>
+        <v>127295161</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377441</v>
+        <v>377576</v>
       </c>
       <c r="R11" t="n">
-        <v>6744357</v>
+        <v>6744414</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B21" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295138</v>
+        <v>127295100</v>
       </c>
       <c r="B30" t="n">
-        <v>79050</v>
+        <v>78776</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377211</v>
+        <v>377499</v>
       </c>
       <c r="R30" t="n">
-        <v>6744196</v>
+        <v>6744545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295100</v>
+        <v>127295165</v>
       </c>
       <c r="B31" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377499</v>
+        <v>377640</v>
       </c>
       <c r="R31" t="n">
-        <v>6744545</v>
+        <v>6744349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295158</v>
+        <v>127295116</v>
       </c>
       <c r="B32" t="n">
-        <v>79018</v>
+        <v>79607</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377488</v>
+        <v>377494</v>
       </c>
       <c r="R32" t="n">
-        <v>6744404</v>
+        <v>6744143</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295165</v>
+        <v>127295105</v>
       </c>
       <c r="B33" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377640</v>
+        <v>377468</v>
       </c>
       <c r="R33" t="n">
-        <v>6744349</v>
+        <v>6744527</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295116</v>
+        <v>127295138</v>
       </c>
       <c r="B34" t="n">
-        <v>79607</v>
+        <v>79050</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377494</v>
+        <v>377211</v>
       </c>
       <c r="R34" t="n">
-        <v>6744143</v>
+        <v>6744196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295105</v>
+        <v>127295158</v>
       </c>
       <c r="B35" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377468</v>
+        <v>377488</v>
       </c>
       <c r="R35" t="n">
-        <v>6744527</v>
+        <v>6744404</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B39" t="n">
-        <v>78777</v>
+        <v>79050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R39" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B40" t="n">
-        <v>79050</v>
+        <v>78777</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R40" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4475,7 +4475,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295142</v>
+        <v>127295135</v>
       </c>
       <c r="B41" t="n">
         <v>79018</v>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377328</v>
+        <v>377206</v>
       </c>
       <c r="R41" t="n">
-        <v>6744286</v>
+        <v>6744255</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295135</v>
+        <v>127295142</v>
       </c>
       <c r="B42" t="n">
         <v>79018</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>377206</v>
+        <v>377328</v>
       </c>
       <c r="R42" t="n">
-        <v>6744255</v>
+        <v>6744286</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295133</v>
+        <v>127295154</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377237</v>
+        <v>377487</v>
       </c>
       <c r="R3" t="n">
-        <v>6744276</v>
+        <v>6744422</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +866,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295154</v>
+        <v>127295133</v>
       </c>
       <c r="B4" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377487</v>
+        <v>377237</v>
       </c>
       <c r="R4" t="n">
-        <v>6744422</v>
+        <v>6744276</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295126</v>
+        <v>127295106</v>
       </c>
       <c r="B22" t="n">
-        <v>96700</v>
+        <v>78777</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377213</v>
+        <v>377535</v>
       </c>
       <c r="R22" t="n">
-        <v>6744163</v>
+        <v>6744318</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295162</v>
+        <v>127295126</v>
       </c>
       <c r="B23" t="n">
-        <v>78685</v>
+        <v>96700</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377576</v>
+        <v>377213</v>
       </c>
       <c r="R23" t="n">
-        <v>6744414</v>
+        <v>6744163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295160</v>
+        <v>127295162</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377463</v>
+        <v>377576</v>
       </c>
       <c r="R24" t="n">
-        <v>6744378</v>
+        <v>6744414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295140</v>
+        <v>127295160</v>
       </c>
       <c r="B25" t="n">
         <v>79018</v>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377379</v>
+        <v>377463</v>
       </c>
       <c r="R25" t="n">
-        <v>6744330</v>
+        <v>6744378</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295106</v>
+        <v>127295140</v>
       </c>
       <c r="B26" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377535</v>
+        <v>377379</v>
       </c>
       <c r="R26" t="n">
-        <v>6744318</v>
+        <v>6744330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295115</v>
+        <v>127295118</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>78777</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377494</v>
+        <v>377523</v>
       </c>
       <c r="R28" t="n">
-        <v>6744143</v>
+        <v>6744132</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295118</v>
+        <v>127295115</v>
       </c>
       <c r="B29" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377523</v>
+        <v>377494</v>
       </c>
       <c r="R29" t="n">
-        <v>6744132</v>
+        <v>6744143</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295143</v>
+        <v>127295167</v>
       </c>
       <c r="B48" t="n">
-        <v>78685</v>
+        <v>79636</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377379</v>
+        <v>377647</v>
       </c>
       <c r="R48" t="n">
-        <v>6744326</v>
+        <v>6744358</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5233,6 +5233,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5348,10 +5349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295167</v>
+        <v>127295143</v>
       </c>
       <c r="B50" t="n">
-        <v>79636</v>
+        <v>78685</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5359,21 +5360,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5383,10 +5384,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377647</v>
+        <v>377379</v>
       </c>
       <c r="R50" t="n">
-        <v>6744358</v>
+        <v>6744326</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5427,7 +5428,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R5" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R6" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295163</v>
+        <v>127295161</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377441</v>
+        <v>377576</v>
       </c>
       <c r="R9" t="n">
-        <v>6744357</v>
+        <v>6744414</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295161</v>
+        <v>127295163</v>
       </c>
       <c r="B11" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377576</v>
+        <v>377441</v>
       </c>
       <c r="R11" t="n">
-        <v>6744414</v>
+        <v>6744357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295147</v>
+        <v>127295136</v>
       </c>
       <c r="B12" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377575</v>
+        <v>377216</v>
       </c>
       <c r="R12" t="n">
-        <v>6744364</v>
+        <v>6744274</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295136</v>
+        <v>127295147</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377216</v>
+        <v>377575</v>
       </c>
       <c r="R13" t="n">
-        <v>6744274</v>
+        <v>6744364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295106</v>
+        <v>127295160</v>
       </c>
       <c r="B22" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377535</v>
+        <v>377463</v>
       </c>
       <c r="R22" t="n">
-        <v>6744318</v>
+        <v>6744378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295126</v>
+        <v>127295140</v>
       </c>
       <c r="B23" t="n">
-        <v>96700</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377213</v>
+        <v>377379</v>
       </c>
       <c r="R23" t="n">
-        <v>6744163</v>
+        <v>6744330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295162</v>
+        <v>127295126</v>
       </c>
       <c r="B24" t="n">
-        <v>78685</v>
+        <v>96700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377576</v>
+        <v>377213</v>
       </c>
       <c r="R24" t="n">
-        <v>6744414</v>
+        <v>6744163</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295160</v>
+        <v>127295162</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>78685</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377463</v>
+        <v>377576</v>
       </c>
       <c r="R25" t="n">
-        <v>6744378</v>
+        <v>6744414</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295140</v>
+        <v>127295106</v>
       </c>
       <c r="B26" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377379</v>
+        <v>377535</v>
       </c>
       <c r="R26" t="n">
-        <v>6744330</v>
+        <v>6744318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295164</v>
+        <v>127295118</v>
       </c>
       <c r="B27" t="n">
-        <v>79050</v>
+        <v>78777</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377671</v>
+        <v>377523</v>
       </c>
       <c r="R27" t="n">
-        <v>6744350</v>
+        <v>6744132</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295118</v>
+        <v>127295115</v>
       </c>
       <c r="B28" t="n">
-        <v>78777</v>
+        <v>79636</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377523</v>
+        <v>377494</v>
       </c>
       <c r="R28" t="n">
-        <v>6744132</v>
+        <v>6744143</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295115</v>
+        <v>127295164</v>
       </c>
       <c r="B29" t="n">
-        <v>79636</v>
+        <v>79050</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377494</v>
+        <v>377671</v>
       </c>
       <c r="R29" t="n">
-        <v>6744143</v>
+        <v>6744350</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295100</v>
+        <v>127295158</v>
       </c>
       <c r="B30" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377499</v>
+        <v>377488</v>
       </c>
       <c r="R30" t="n">
-        <v>6744545</v>
+        <v>6744404</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295116</v>
+        <v>127295100</v>
       </c>
       <c r="B32" t="n">
-        <v>79607</v>
+        <v>78776</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377494</v>
+        <v>377499</v>
       </c>
       <c r="R32" t="n">
-        <v>6744143</v>
+        <v>6744545</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295105</v>
+        <v>127295116</v>
       </c>
       <c r="B33" t="n">
-        <v>78777</v>
+        <v>79607</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377468</v>
+        <v>377494</v>
       </c>
       <c r="R33" t="n">
-        <v>6744527</v>
+        <v>6744143</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295138</v>
+        <v>127295105</v>
       </c>
       <c r="B34" t="n">
-        <v>79050</v>
+        <v>78777</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377211</v>
+        <v>377468</v>
       </c>
       <c r="R34" t="n">
-        <v>6744196</v>
+        <v>6744527</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295158</v>
+        <v>127295138</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79050</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377488</v>
+        <v>377211</v>
       </c>
       <c r="R35" t="n">
-        <v>6744404</v>
+        <v>6744196</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295109</v>
+        <v>127295151</v>
       </c>
       <c r="B36" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>377479</v>
+        <v>377506</v>
       </c>
       <c r="R36" t="n">
-        <v>6744536</v>
+        <v>6744399</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295151</v>
+        <v>127295109</v>
       </c>
       <c r="B37" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>377506</v>
+        <v>377479</v>
       </c>
       <c r="R37" t="n">
-        <v>6744399</v>
+        <v>6744536</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B39" t="n">
-        <v>79050</v>
+        <v>78777</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R39" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B40" t="n">
-        <v>78777</v>
+        <v>79050</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R40" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295135</v>
+        <v>127295107</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377206</v>
+        <v>377557</v>
       </c>
       <c r="R41" t="n">
-        <v>6744255</v>
+        <v>6744301</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295107</v>
+        <v>127295135</v>
       </c>
       <c r="B43" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>377557</v>
+        <v>377206</v>
       </c>
       <c r="R43" t="n">
-        <v>6744301</v>
+        <v>6744255</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B44" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R44" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B45" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R45" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295167</v>
+        <v>127295111</v>
       </c>
       <c r="B48" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377647</v>
+        <v>377466</v>
       </c>
       <c r="R48" t="n">
-        <v>6744358</v>
+        <v>6744500</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5233,7 +5233,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5252,10 +5251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295111</v>
+        <v>127295167</v>
       </c>
       <c r="B49" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5263,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5287,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377466</v>
+        <v>377647</v>
       </c>
       <c r="R49" t="n">
-        <v>6744500</v>
+        <v>6744358</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5331,6 +5330,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B44" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R44" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B45" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R45" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295154</v>
+        <v>127295133</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377487</v>
+        <v>377237</v>
       </c>
       <c r="R3" t="n">
-        <v>6744422</v>
+        <v>6744276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295133</v>
+        <v>127295154</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377237</v>
+        <v>377487</v>
       </c>
       <c r="R4" t="n">
-        <v>6744276</v>
+        <v>6744422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -985,7 +985,7 @@
         <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295119</v>
+        <v>127295163</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377599</v>
+        <v>377441</v>
       </c>
       <c r="R7" t="n">
-        <v>6744109</v>
+        <v>6744357</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295150</v>
+        <v>127295161</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>78779</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377507</v>
+        <v>377576</v>
       </c>
       <c r="R8" t="n">
-        <v>6744400</v>
+        <v>6744414</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295161</v>
+        <v>127295119</v>
       </c>
       <c r="B9" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377576</v>
+        <v>377599</v>
       </c>
       <c r="R9" t="n">
-        <v>6744414</v>
+        <v>6744109</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295145</v>
+        <v>127295150</v>
       </c>
       <c r="B10" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377331</v>
+        <v>377507</v>
       </c>
       <c r="R10" t="n">
-        <v>6744278</v>
+        <v>6744400</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295163</v>
+        <v>127295145</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377441</v>
+        <v>377331</v>
       </c>
       <c r="R11" t="n">
-        <v>6744357</v>
+        <v>6744278</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
         <v>127295136</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127295147</v>
       </c>
       <c r="B13" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295101</v>
+        <v>127295114</v>
       </c>
       <c r="B14" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377493</v>
+        <v>377455</v>
       </c>
       <c r="R14" t="n">
-        <v>6744550</v>
+        <v>6744199</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295114</v>
+        <v>127295101</v>
       </c>
       <c r="B15" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377455</v>
+        <v>377493</v>
       </c>
       <c r="R15" t="n">
-        <v>6744199</v>
+        <v>6744550</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>127295144</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295117</v>
+        <v>127295134</v>
       </c>
       <c r="B17" t="n">
-        <v>79018</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>377588</v>
+        <v>377206</v>
       </c>
       <c r="R17" t="n">
-        <v>6743996</v>
+        <v>6744255</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295134</v>
+        <v>127295117</v>
       </c>
       <c r="B18" t="n">
-        <v>79042</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377206</v>
+        <v>377588</v>
       </c>
       <c r="R18" t="n">
-        <v>6744255</v>
+        <v>6743996</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
         <v>127295152</v>
       </c>
       <c r="B19" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295160</v>
+        <v>127295140</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377463</v>
+        <v>377379</v>
       </c>
       <c r="R22" t="n">
-        <v>6744378</v>
+        <v>6744330</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295140</v>
+        <v>127295126</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>96702</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377379</v>
+        <v>377213</v>
       </c>
       <c r="R23" t="n">
-        <v>6744330</v>
+        <v>6744163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295126</v>
+        <v>127295162</v>
       </c>
       <c r="B24" t="n">
-        <v>96700</v>
+        <v>78687</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377213</v>
+        <v>377576</v>
       </c>
       <c r="R24" t="n">
-        <v>6744163</v>
+        <v>6744414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295162</v>
+        <v>127295160</v>
       </c>
       <c r="B25" t="n">
-        <v>78685</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377576</v>
+        <v>377463</v>
       </c>
       <c r="R25" t="n">
-        <v>6744414</v>
+        <v>6744378</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3023,7 +3023,7 @@
         <v>127295106</v>
       </c>
       <c r="B26" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295118</v>
+        <v>127295115</v>
       </c>
       <c r="B27" t="n">
-        <v>78777</v>
+        <v>79638</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377523</v>
+        <v>377494</v>
       </c>
       <c r="R27" t="n">
-        <v>6744132</v>
+        <v>6744143</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295115</v>
+        <v>127295164</v>
       </c>
       <c r="B28" t="n">
-        <v>79636</v>
+        <v>79052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377494</v>
+        <v>377671</v>
       </c>
       <c r="R28" t="n">
-        <v>6744143</v>
+        <v>6744350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295164</v>
+        <v>127295118</v>
       </c>
       <c r="B29" t="n">
-        <v>79050</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377671</v>
+        <v>377523</v>
       </c>
       <c r="R29" t="n">
-        <v>6744350</v>
+        <v>6744132</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295158</v>
+        <v>127295138</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>79052</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377488</v>
+        <v>377211</v>
       </c>
       <c r="R30" t="n">
-        <v>6744404</v>
+        <v>6744196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295165</v>
+        <v>127295116</v>
       </c>
       <c r="B31" t="n">
-        <v>79018</v>
+        <v>79609</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377640</v>
+        <v>377494</v>
       </c>
       <c r="R31" t="n">
-        <v>6744349</v>
+        <v>6744143</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295100</v>
+        <v>127295105</v>
       </c>
       <c r="B32" t="n">
-        <v>78776</v>
+        <v>78779</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377499</v>
+        <v>377468</v>
       </c>
       <c r="R32" t="n">
-        <v>6744545</v>
+        <v>6744527</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295116</v>
+        <v>127295165</v>
       </c>
       <c r="B33" t="n">
-        <v>79607</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377494</v>
+        <v>377640</v>
       </c>
       <c r="R33" t="n">
-        <v>6744143</v>
+        <v>6744349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295105</v>
+        <v>127295158</v>
       </c>
       <c r="B34" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377468</v>
+        <v>377488</v>
       </c>
       <c r="R34" t="n">
-        <v>6744527</v>
+        <v>6744404</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295138</v>
+        <v>127295100</v>
       </c>
       <c r="B35" t="n">
-        <v>79050</v>
+        <v>78778</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377211</v>
+        <v>377499</v>
       </c>
       <c r="R35" t="n">
-        <v>6744196</v>
+        <v>6744545</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295151</v>
+        <v>127295108</v>
       </c>
       <c r="B36" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>377506</v>
+        <v>377545</v>
       </c>
       <c r="R36" t="n">
-        <v>6744399</v>
+        <v>6744314</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
         <v>127295109</v>
       </c>
       <c r="B37" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295108</v>
+        <v>127295151</v>
       </c>
       <c r="B38" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>377545</v>
+        <v>377506</v>
       </c>
       <c r="R38" t="n">
-        <v>6744314</v>
+        <v>6744399</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B39" t="n">
-        <v>78777</v>
+        <v>79052</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R39" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B40" t="n">
-        <v>79050</v>
+        <v>78779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R40" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295107</v>
+        <v>127295142</v>
       </c>
       <c r="B41" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377557</v>
+        <v>377328</v>
       </c>
       <c r="R41" t="n">
-        <v>6744301</v>
+        <v>6744286</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295142</v>
+        <v>127295135</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>377328</v>
+        <v>377206</v>
       </c>
       <c r="R42" t="n">
-        <v>6744286</v>
+        <v>6744255</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295135</v>
+        <v>127295107</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>377206</v>
+        <v>377557</v>
       </c>
       <c r="R43" t="n">
-        <v>6744255</v>
+        <v>6744301</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4769,7 +4769,7 @@
         <v>127295155</v>
       </c>
       <c r="B44" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>127295104</v>
       </c>
       <c r="B45" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295132</v>
+        <v>127295121</v>
       </c>
       <c r="B46" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4971,21 +4971,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>377208</v>
+        <v>377523</v>
       </c>
       <c r="R46" t="n">
-        <v>6744241</v>
+        <v>6744136</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295121</v>
+        <v>127295132</v>
       </c>
       <c r="B47" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>377523</v>
+        <v>377208</v>
       </c>
       <c r="R47" t="n">
-        <v>6744136</v>
+        <v>6744241</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295111</v>
+        <v>127295143</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>78687</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377466</v>
+        <v>377379</v>
       </c>
       <c r="R48" t="n">
-        <v>6744500</v>
+        <v>6744326</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295167</v>
+        <v>127295111</v>
       </c>
       <c r="B49" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377647</v>
+        <v>377466</v>
       </c>
       <c r="R49" t="n">
-        <v>6744358</v>
+        <v>6744500</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5330,7 +5330,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5349,10 +5348,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295143</v>
+        <v>127295167</v>
       </c>
       <c r="B50" t="n">
-        <v>78685</v>
+        <v>79638</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5360,21 +5359,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5384,10 +5383,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377379</v>
+        <v>377647</v>
       </c>
       <c r="R50" t="n">
-        <v>6744326</v>
+        <v>6744358</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5428,6 +5427,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R5" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R6" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,7 +1176,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295163</v>
+        <v>127295145</v>
       </c>
       <c r="B7" t="n">
         <v>79020</v>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377441</v>
+        <v>377331</v>
       </c>
       <c r="R7" t="n">
-        <v>6744357</v>
+        <v>6744278</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295161</v>
+        <v>127295163</v>
       </c>
       <c r="B8" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377576</v>
+        <v>377441</v>
       </c>
       <c r="R8" t="n">
-        <v>6744414</v>
+        <v>6744357</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295145</v>
+        <v>127295161</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377331</v>
+        <v>377576</v>
       </c>
       <c r="R11" t="n">
-        <v>6744278</v>
+        <v>6744414</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2632,7 +2632,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295140</v>
+        <v>127295160</v>
       </c>
       <c r="B22" t="n">
         <v>79020</v>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377379</v>
+        <v>377463</v>
       </c>
       <c r="R22" t="n">
-        <v>6744330</v>
+        <v>6744378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295126</v>
+        <v>127295140</v>
       </c>
       <c r="B23" t="n">
-        <v>96702</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377213</v>
+        <v>377379</v>
       </c>
       <c r="R23" t="n">
-        <v>6744163</v>
+        <v>6744330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295162</v>
+        <v>127295126</v>
       </c>
       <c r="B24" t="n">
-        <v>78687</v>
+        <v>96702</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377576</v>
+        <v>377213</v>
       </c>
       <c r="R24" t="n">
-        <v>6744414</v>
+        <v>6744163</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295160</v>
+        <v>127295162</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377463</v>
+        <v>377576</v>
       </c>
       <c r="R25" t="n">
-        <v>6744378</v>
+        <v>6744414</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295115</v>
+        <v>127295118</v>
       </c>
       <c r="B27" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377494</v>
+        <v>377523</v>
       </c>
       <c r="R27" t="n">
-        <v>6744143</v>
+        <v>6744132</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295118</v>
+        <v>127295115</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377523</v>
+        <v>377494</v>
       </c>
       <c r="R29" t="n">
-        <v>6744132</v>
+        <v>6744143</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295116</v>
+        <v>127295165</v>
       </c>
       <c r="B31" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377494</v>
+        <v>377640</v>
       </c>
       <c r="R31" t="n">
-        <v>6744143</v>
+        <v>6744349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295105</v>
+        <v>127295158</v>
       </c>
       <c r="B32" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377468</v>
+        <v>377488</v>
       </c>
       <c r="R32" t="n">
-        <v>6744527</v>
+        <v>6744404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295165</v>
+        <v>127295100</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377640</v>
+        <v>377499</v>
       </c>
       <c r="R33" t="n">
-        <v>6744349</v>
+        <v>6744545</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295158</v>
+        <v>127295116</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377488</v>
+        <v>377494</v>
       </c>
       <c r="R34" t="n">
-        <v>6744404</v>
+        <v>6744143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295100</v>
+        <v>127295105</v>
       </c>
       <c r="B35" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377499</v>
+        <v>377468</v>
       </c>
       <c r="R35" t="n">
-        <v>6744545</v>
+        <v>6744527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B39" t="n">
-        <v>79052</v>
+        <v>78779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R39" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B40" t="n">
-        <v>78779</v>
+        <v>79052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R40" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B44" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R44" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B45" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R45" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295121</v>
+        <v>127295132</v>
       </c>
       <c r="B46" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4971,21 +4971,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>377523</v>
+        <v>377208</v>
       </c>
       <c r="R46" t="n">
-        <v>6744136</v>
+        <v>6744241</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295132</v>
+        <v>127295121</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>377208</v>
+        <v>377523</v>
       </c>
       <c r="R47" t="n">
-        <v>6744241</v>
+        <v>6744136</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295133</v>
+        <v>127295154</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377237</v>
+        <v>377487</v>
       </c>
       <c r="R3" t="n">
-        <v>6744276</v>
+        <v>6744422</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +866,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295154</v>
+        <v>127295133</v>
       </c>
       <c r="B4" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377487</v>
+        <v>377237</v>
       </c>
       <c r="R4" t="n">
-        <v>6744422</v>
+        <v>6744276</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295145</v>
+        <v>127295161</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377331</v>
+        <v>377576</v>
       </c>
       <c r="R7" t="n">
-        <v>6744278</v>
+        <v>6744414</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,7 +1273,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295163</v>
+        <v>127295145</v>
       </c>
       <c r="B8" t="n">
         <v>79020</v>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377441</v>
+        <v>377331</v>
       </c>
       <c r="R8" t="n">
-        <v>6744357</v>
+        <v>6744278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295119</v>
+        <v>127295163</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377599</v>
+        <v>377441</v>
       </c>
       <c r="R9" t="n">
-        <v>6744109</v>
+        <v>6744357</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,7 +1467,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295150</v>
+        <v>127295119</v>
       </c>
       <c r="B10" t="n">
         <v>79638</v>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377507</v>
+        <v>377599</v>
       </c>
       <c r="R10" t="n">
-        <v>6744400</v>
+        <v>6744109</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295161</v>
+        <v>127295150</v>
       </c>
       <c r="B11" t="n">
-        <v>78779</v>
+        <v>79638</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377576</v>
+        <v>377507</v>
       </c>
       <c r="R11" t="n">
-        <v>6744414</v>
+        <v>6744400</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295136</v>
+        <v>127295147</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377216</v>
+        <v>377575</v>
       </c>
       <c r="R12" t="n">
-        <v>6744274</v>
+        <v>6744364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295147</v>
+        <v>127295114</v>
       </c>
       <c r="B13" t="n">
         <v>79638</v>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377575</v>
+        <v>377455</v>
       </c>
       <c r="R13" t="n">
-        <v>6744364</v>
+        <v>6744199</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295114</v>
+        <v>127295101</v>
       </c>
       <c r="B14" t="n">
         <v>79638</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377455</v>
+        <v>377493</v>
       </c>
       <c r="R14" t="n">
-        <v>6744199</v>
+        <v>6744550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295101</v>
+        <v>127295136</v>
       </c>
       <c r="B15" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377493</v>
+        <v>377216</v>
       </c>
       <c r="R15" t="n">
-        <v>6744550</v>
+        <v>6744274</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295126</v>
+        <v>127295106</v>
       </c>
       <c r="B24" t="n">
-        <v>96702</v>
+        <v>78779</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377213</v>
+        <v>377535</v>
       </c>
       <c r="R24" t="n">
-        <v>6744163</v>
+        <v>6744318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295162</v>
+        <v>127295126</v>
       </c>
       <c r="B25" t="n">
-        <v>78687</v>
+        <v>96702</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377576</v>
+        <v>377213</v>
       </c>
       <c r="R25" t="n">
-        <v>6744414</v>
+        <v>6744163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295106</v>
+        <v>127295162</v>
       </c>
       <c r="B26" t="n">
-        <v>78779</v>
+        <v>78687</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377535</v>
+        <v>377576</v>
       </c>
       <c r="R26" t="n">
-        <v>6744318</v>
+        <v>6744414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295138</v>
+        <v>127295116</v>
       </c>
       <c r="B30" t="n">
-        <v>79052</v>
+        <v>79609</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377211</v>
+        <v>377494</v>
       </c>
       <c r="R30" t="n">
-        <v>6744196</v>
+        <v>6744143</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295165</v>
+        <v>127295105</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377640</v>
+        <v>377468</v>
       </c>
       <c r="R31" t="n">
-        <v>6744349</v>
+        <v>6744527</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,7 +3602,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295158</v>
+        <v>127295165</v>
       </c>
       <c r="B32" t="n">
         <v>79020</v>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377488</v>
+        <v>377640</v>
       </c>
       <c r="R32" t="n">
-        <v>6744404</v>
+        <v>6744349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295100</v>
+        <v>127295158</v>
       </c>
       <c r="B33" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377499</v>
+        <v>377488</v>
       </c>
       <c r="R33" t="n">
-        <v>6744545</v>
+        <v>6744404</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295116</v>
+        <v>127295100</v>
       </c>
       <c r="B34" t="n">
-        <v>79609</v>
+        <v>78778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377494</v>
+        <v>377499</v>
       </c>
       <c r="R34" t="n">
-        <v>6744143</v>
+        <v>6744545</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295105</v>
+        <v>127295138</v>
       </c>
       <c r="B35" t="n">
-        <v>78779</v>
+        <v>79052</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377468</v>
+        <v>377211</v>
       </c>
       <c r="R35" t="n">
-        <v>6744527</v>
+        <v>6744196</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295109</v>
+        <v>127295151</v>
       </c>
       <c r="B37" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>377479</v>
+        <v>377506</v>
       </c>
       <c r="R37" t="n">
-        <v>6744536</v>
+        <v>6744399</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295151</v>
+        <v>127295109</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>377506</v>
+        <v>377479</v>
       </c>
       <c r="R38" t="n">
-        <v>6744399</v>
+        <v>6744536</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B39" t="n">
-        <v>78779</v>
+        <v>79052</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R39" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B40" t="n">
-        <v>79052</v>
+        <v>78779</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R40" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295154</v>
+        <v>127295133</v>
       </c>
       <c r="B3" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377487</v>
+        <v>377237</v>
       </c>
       <c r="R3" t="n">
-        <v>6744422</v>
+        <v>6744276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295133</v>
+        <v>127295154</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377237</v>
+        <v>377487</v>
       </c>
       <c r="R4" t="n">
-        <v>6744276</v>
+        <v>6744422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R5" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R6" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295161</v>
+        <v>127295145</v>
       </c>
       <c r="B7" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377576</v>
+        <v>377331</v>
       </c>
       <c r="R7" t="n">
-        <v>6744414</v>
+        <v>6744278</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295145</v>
+        <v>127295150</v>
       </c>
       <c r="B8" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377331</v>
+        <v>377507</v>
       </c>
       <c r="R8" t="n">
-        <v>6744278</v>
+        <v>6744400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295150</v>
+        <v>127295161</v>
       </c>
       <c r="B11" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377507</v>
+        <v>377576</v>
       </c>
       <c r="R11" t="n">
-        <v>6744400</v>
+        <v>6744414</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295114</v>
+        <v>127295136</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377455</v>
+        <v>377216</v>
       </c>
       <c r="R13" t="n">
-        <v>6744199</v>
+        <v>6744274</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295101</v>
+        <v>127295114</v>
       </c>
       <c r="B14" t="n">
         <v>79638</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377493</v>
+        <v>377455</v>
       </c>
       <c r="R14" t="n">
-        <v>6744550</v>
+        <v>6744199</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295136</v>
+        <v>127295101</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377216</v>
+        <v>377493</v>
       </c>
       <c r="R15" t="n">
-        <v>6744274</v>
+        <v>6744550</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295134</v>
+        <v>127295117</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79020</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>377206</v>
+        <v>377588</v>
       </c>
       <c r="R17" t="n">
-        <v>6744255</v>
+        <v>6743996</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295117</v>
+        <v>127295134</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377588</v>
+        <v>377206</v>
       </c>
       <c r="R18" t="n">
-        <v>6743996</v>
+        <v>6744255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B20" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B21" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2632,7 +2632,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295160</v>
+        <v>127295140</v>
       </c>
       <c r="B22" t="n">
         <v>79020</v>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377463</v>
+        <v>377379</v>
       </c>
       <c r="R22" t="n">
-        <v>6744378</v>
+        <v>6744330</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295140</v>
+        <v>127295126</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>96702</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377379</v>
+        <v>377213</v>
       </c>
       <c r="R23" t="n">
-        <v>6744330</v>
+        <v>6744163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295106</v>
+        <v>127295160</v>
       </c>
       <c r="B24" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377535</v>
+        <v>377463</v>
       </c>
       <c r="R24" t="n">
-        <v>6744318</v>
+        <v>6744378</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295126</v>
+        <v>127295162</v>
       </c>
       <c r="B25" t="n">
-        <v>96702</v>
+        <v>78687</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377213</v>
+        <v>377576</v>
       </c>
       <c r="R25" t="n">
-        <v>6744163</v>
+        <v>6744414</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295162</v>
+        <v>127295106</v>
       </c>
       <c r="B26" t="n">
-        <v>78687</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377576</v>
+        <v>377535</v>
       </c>
       <c r="R26" t="n">
-        <v>6744414</v>
+        <v>6744318</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295118</v>
+        <v>127295164</v>
       </c>
       <c r="B27" t="n">
-        <v>78779</v>
+        <v>79052</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377523</v>
+        <v>377671</v>
       </c>
       <c r="R27" t="n">
-        <v>6744132</v>
+        <v>6744350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295164</v>
+        <v>127295115</v>
       </c>
       <c r="B28" t="n">
-        <v>79052</v>
+        <v>79638</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377671</v>
+        <v>377494</v>
       </c>
       <c r="R28" t="n">
-        <v>6744350</v>
+        <v>6744143</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295115</v>
+        <v>127295118</v>
       </c>
       <c r="B29" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377494</v>
+        <v>377523</v>
       </c>
       <c r="R29" t="n">
-        <v>6744143</v>
+        <v>6744132</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295116</v>
+        <v>127295100</v>
       </c>
       <c r="B30" t="n">
-        <v>79609</v>
+        <v>78778</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377494</v>
+        <v>377499</v>
       </c>
       <c r="R30" t="n">
-        <v>6744143</v>
+        <v>6744545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295105</v>
+        <v>127295158</v>
       </c>
       <c r="B31" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377468</v>
+        <v>377488</v>
       </c>
       <c r="R31" t="n">
-        <v>6744527</v>
+        <v>6744404</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295158</v>
+        <v>127295138</v>
       </c>
       <c r="B33" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377488</v>
+        <v>377211</v>
       </c>
       <c r="R33" t="n">
-        <v>6744404</v>
+        <v>6744196</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295100</v>
+        <v>127295116</v>
       </c>
       <c r="B34" t="n">
-        <v>78778</v>
+        <v>79609</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377499</v>
+        <v>377494</v>
       </c>
       <c r="R34" t="n">
-        <v>6744545</v>
+        <v>6744143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295138</v>
+        <v>127295105</v>
       </c>
       <c r="B35" t="n">
-        <v>79052</v>
+        <v>78779</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377211</v>
+        <v>377468</v>
       </c>
       <c r="R35" t="n">
-        <v>6744196</v>
+        <v>6744527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295108</v>
+        <v>127295151</v>
       </c>
       <c r="B36" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>377545</v>
+        <v>377506</v>
       </c>
       <c r="R36" t="n">
-        <v>6744314</v>
+        <v>6744399</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295151</v>
+        <v>127295109</v>
       </c>
       <c r="B37" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>377506</v>
+        <v>377479</v>
       </c>
       <c r="R37" t="n">
-        <v>6744399</v>
+        <v>6744536</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295109</v>
+        <v>127295108</v>
       </c>
       <c r="B38" t="n">
-        <v>79638</v>
+        <v>78779</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>377479</v>
+        <v>377545</v>
       </c>
       <c r="R38" t="n">
-        <v>6744536</v>
+        <v>6744314</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B39" t="n">
-        <v>79052</v>
+        <v>78779</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R39" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B40" t="n">
-        <v>78779</v>
+        <v>79052</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R40" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B44" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R44" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B45" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R45" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295143</v>
+        <v>127295167</v>
       </c>
       <c r="B48" t="n">
-        <v>78687</v>
+        <v>79638</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377379</v>
+        <v>377647</v>
       </c>
       <c r="R48" t="n">
-        <v>6744326</v>
+        <v>6744358</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5233,6 +5233,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5251,10 +5252,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295111</v>
+        <v>127295143</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5262,21 +5263,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5286,10 +5287,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377466</v>
+        <v>377379</v>
       </c>
       <c r="R49" t="n">
-        <v>6744500</v>
+        <v>6744326</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5348,10 +5349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295167</v>
+        <v>127295111</v>
       </c>
       <c r="B50" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5359,21 +5360,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5383,10 +5384,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377647</v>
+        <v>377466</v>
       </c>
       <c r="R50" t="n">
-        <v>6744358</v>
+        <v>6744500</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5427,7 +5428,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B5" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R5" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B6" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R6" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295147</v>
+        <v>127295136</v>
       </c>
       <c r="B12" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377575</v>
+        <v>377216</v>
       </c>
       <c r="R12" t="n">
-        <v>6744364</v>
+        <v>6744274</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295136</v>
+        <v>127295101</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377216</v>
+        <v>377493</v>
       </c>
       <c r="R13" t="n">
-        <v>6744274</v>
+        <v>6744550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295114</v>
+        <v>127295147</v>
       </c>
       <c r="B14" t="n">
         <v>79638</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377455</v>
+        <v>377575</v>
       </c>
       <c r="R14" t="n">
-        <v>6744199</v>
+        <v>6744364</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295101</v>
+        <v>127295114</v>
       </c>
       <c r="B15" t="n">
         <v>79638</v>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377493</v>
+        <v>377455</v>
       </c>
       <c r="R15" t="n">
-        <v>6744550</v>
+        <v>6744199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295140</v>
+        <v>127295162</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>78687</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377379</v>
+        <v>377576</v>
       </c>
       <c r="R22" t="n">
-        <v>6744330</v>
+        <v>6744414</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2732,7 +2732,7 @@
         <v>127295126</v>
       </c>
       <c r="B23" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295162</v>
+        <v>127295140</v>
       </c>
       <c r="B25" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377576</v>
+        <v>377379</v>
       </c>
       <c r="R25" t="n">
-        <v>6744414</v>
+        <v>6744330</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295100</v>
+        <v>127295105</v>
       </c>
       <c r="B30" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377499</v>
+        <v>377468</v>
       </c>
       <c r="R30" t="n">
-        <v>6744545</v>
+        <v>6744527</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295165</v>
+        <v>127295138</v>
       </c>
       <c r="B32" t="n">
-        <v>79020</v>
+        <v>79052</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377640</v>
+        <v>377211</v>
       </c>
       <c r="R32" t="n">
-        <v>6744349</v>
+        <v>6744196</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295138</v>
+        <v>127295100</v>
       </c>
       <c r="B33" t="n">
-        <v>79052</v>
+        <v>78778</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377211</v>
+        <v>377499</v>
       </c>
       <c r="R33" t="n">
-        <v>6744196</v>
+        <v>6744545</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295116</v>
+        <v>127295165</v>
       </c>
       <c r="B34" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377494</v>
+        <v>377640</v>
       </c>
       <c r="R34" t="n">
-        <v>6744143</v>
+        <v>6744349</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295105</v>
+        <v>127295116</v>
       </c>
       <c r="B35" t="n">
-        <v>78779</v>
+        <v>79609</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377468</v>
+        <v>377494</v>
       </c>
       <c r="R35" t="n">
-        <v>6744527</v>
+        <v>6744143</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295167</v>
+        <v>127295143</v>
       </c>
       <c r="B48" t="n">
-        <v>79638</v>
+        <v>78687</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377647</v>
+        <v>377379</v>
       </c>
       <c r="R48" t="n">
-        <v>6744358</v>
+        <v>6744326</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5233,7 +5233,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5252,10 +5251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295143</v>
+        <v>127295111</v>
       </c>
       <c r="B49" t="n">
-        <v>78687</v>
+        <v>79020</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5263,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5287,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377379</v>
+        <v>377466</v>
       </c>
       <c r="R49" t="n">
-        <v>6744326</v>
+        <v>6744500</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5349,10 +5348,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295111</v>
+        <v>127295167</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5360,21 +5359,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5384,10 +5383,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377466</v>
+        <v>377647</v>
       </c>
       <c r="R50" t="n">
-        <v>6744500</v>
+        <v>6744358</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5428,6 +5427,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127295133</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127295154</v>
       </c>
       <c r="B4" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R5" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R6" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295145</v>
+        <v>127295119</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377331</v>
+        <v>377599</v>
       </c>
       <c r="R7" t="n">
-        <v>6744278</v>
+        <v>6744109</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295150</v>
+        <v>127295145</v>
       </c>
       <c r="B8" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377507</v>
+        <v>377331</v>
       </c>
       <c r="R8" t="n">
-        <v>6744400</v>
+        <v>6744278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295163</v>
+        <v>127295150</v>
       </c>
       <c r="B9" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377441</v>
+        <v>377507</v>
       </c>
       <c r="R9" t="n">
-        <v>6744357</v>
+        <v>6744400</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295119</v>
+        <v>127295163</v>
       </c>
       <c r="B10" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377599</v>
+        <v>377441</v>
       </c>
       <c r="R10" t="n">
-        <v>6744109</v>
+        <v>6744357</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1567,7 +1567,7 @@
         <v>127295161</v>
       </c>
       <c r="B11" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295136</v>
+        <v>127295147</v>
       </c>
       <c r="B12" t="n">
-        <v>79020</v>
+        <v>79641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377216</v>
+        <v>377575</v>
       </c>
       <c r="R12" t="n">
-        <v>6744274</v>
+        <v>6744364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295101</v>
+        <v>127295136</v>
       </c>
       <c r="B13" t="n">
-        <v>79638</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377493</v>
+        <v>377216</v>
       </c>
       <c r="R13" t="n">
-        <v>6744550</v>
+        <v>6744274</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295147</v>
+        <v>127295101</v>
       </c>
       <c r="B14" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377575</v>
+        <v>377493</v>
       </c>
       <c r="R14" t="n">
-        <v>6744364</v>
+        <v>6744550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,7 +1955,7 @@
         <v>127295114</v>
       </c>
       <c r="B15" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>127295144</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>127295117</v>
       </c>
       <c r="B17" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>127295134</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79047</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>127295152</v>
       </c>
       <c r="B19" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78779</v>
+        <v>78781</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78778</v>
+        <v>78782</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295162</v>
+        <v>127295126</v>
       </c>
       <c r="B22" t="n">
-        <v>78687</v>
+        <v>96711</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377576</v>
+        <v>377213</v>
       </c>
       <c r="R22" t="n">
-        <v>6744414</v>
+        <v>6744163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295126</v>
+        <v>127295162</v>
       </c>
       <c r="B23" t="n">
-        <v>96708</v>
+        <v>78690</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377213</v>
+        <v>377576</v>
       </c>
       <c r="R23" t="n">
-        <v>6744163</v>
+        <v>6744414</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
         <v>127295160</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>127295140</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>127295106</v>
       </c>
       <c r="B26" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295164</v>
+        <v>127295115</v>
       </c>
       <c r="B27" t="n">
-        <v>79052</v>
+        <v>79641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377671</v>
+        <v>377494</v>
       </c>
       <c r="R27" t="n">
-        <v>6744350</v>
+        <v>6744143</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295115</v>
+        <v>127295118</v>
       </c>
       <c r="B28" t="n">
-        <v>79638</v>
+        <v>78782</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377494</v>
+        <v>377523</v>
       </c>
       <c r="R28" t="n">
-        <v>6744143</v>
+        <v>6744132</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295118</v>
+        <v>127295164</v>
       </c>
       <c r="B29" t="n">
-        <v>78779</v>
+        <v>79055</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377523</v>
+        <v>377671</v>
       </c>
       <c r="R29" t="n">
-        <v>6744132</v>
+        <v>6744350</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295105</v>
+        <v>127295100</v>
       </c>
       <c r="B30" t="n">
-        <v>78779</v>
+        <v>78781</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377468</v>
+        <v>377499</v>
       </c>
       <c r="R30" t="n">
-        <v>6744527</v>
+        <v>6744545</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3508,7 +3508,7 @@
         <v>127295158</v>
       </c>
       <c r="B31" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295138</v>
+        <v>127295165</v>
       </c>
       <c r="B32" t="n">
-        <v>79052</v>
+        <v>79023</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377211</v>
+        <v>377640</v>
       </c>
       <c r="R32" t="n">
-        <v>6744196</v>
+        <v>6744349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295100</v>
+        <v>127295138</v>
       </c>
       <c r="B33" t="n">
-        <v>78778</v>
+        <v>79055</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377499</v>
+        <v>377211</v>
       </c>
       <c r="R33" t="n">
-        <v>6744545</v>
+        <v>6744196</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295165</v>
+        <v>127295116</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>79612</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377640</v>
+        <v>377494</v>
       </c>
       <c r="R34" t="n">
-        <v>6744349</v>
+        <v>6744143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295116</v>
+        <v>127295105</v>
       </c>
       <c r="B35" t="n">
-        <v>79609</v>
+        <v>78782</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377494</v>
+        <v>377468</v>
       </c>
       <c r="R35" t="n">
-        <v>6744143</v>
+        <v>6744527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295151</v>
+        <v>127295108</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>78782</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>377506</v>
+        <v>377545</v>
       </c>
       <c r="R36" t="n">
-        <v>6744399</v>
+        <v>6744314</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
         <v>127295109</v>
       </c>
       <c r="B37" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295108</v>
+        <v>127295151</v>
       </c>
       <c r="B38" t="n">
-        <v>78779</v>
+        <v>79023</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>377545</v>
+        <v>377506</v>
       </c>
       <c r="R38" t="n">
-        <v>6744314</v>
+        <v>6744399</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B39" t="n">
-        <v>78779</v>
+        <v>79055</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R39" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B40" t="n">
-        <v>79052</v>
+        <v>78782</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R40" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
         <v>127295142</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>127295135</v>
       </c>
       <c r="B42" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>127295107</v>
       </c>
       <c r="B43" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B44" t="n">
-        <v>78778</v>
+        <v>78782</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R44" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B45" t="n">
-        <v>78779</v>
+        <v>78781</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R45" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,7 +4963,7 @@
         <v>127295132</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>127295121</v>
       </c>
       <c r="B47" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5157,7 +5157,7 @@
         <v>127295143</v>
       </c>
       <c r="B48" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5254,7 +5254,7 @@
         <v>127295111</v>
       </c>
       <c r="B49" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>127295167</v>
       </c>
       <c r="B50" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>127295133</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>127295154</v>
       </c>
       <c r="B4" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>127295130</v>
       </c>
       <c r="B5" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>127295156</v>
       </c>
       <c r="B6" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>127295119</v>
       </c>
       <c r="B7" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295145</v>
+        <v>127295150</v>
       </c>
       <c r="B8" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377331</v>
+        <v>377507</v>
       </c>
       <c r="R8" t="n">
-        <v>6744278</v>
+        <v>6744400</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295150</v>
+        <v>127295145</v>
       </c>
       <c r="B9" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377507</v>
+        <v>377331</v>
       </c>
       <c r="R9" t="n">
-        <v>6744400</v>
+        <v>6744278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,7 +1470,7 @@
         <v>127295163</v>
       </c>
       <c r="B10" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         <v>127295161</v>
       </c>
       <c r="B11" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295147</v>
+        <v>127295136</v>
       </c>
       <c r="B12" t="n">
-        <v>79641</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377575</v>
+        <v>377216</v>
       </c>
       <c r="R12" t="n">
-        <v>6744364</v>
+        <v>6744274</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295136</v>
+        <v>127295147</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377216</v>
+        <v>377575</v>
       </c>
       <c r="R13" t="n">
-        <v>6744274</v>
+        <v>6744364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295101</v>
+        <v>127295114</v>
       </c>
       <c r="B14" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377493</v>
+        <v>377455</v>
       </c>
       <c r="R14" t="n">
-        <v>6744550</v>
+        <v>6744199</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295114</v>
+        <v>127295101</v>
       </c>
       <c r="B15" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377455</v>
+        <v>377493</v>
       </c>
       <c r="R15" t="n">
-        <v>6744199</v>
+        <v>6744550</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
         <v>127295144</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295117</v>
+        <v>127295134</v>
       </c>
       <c r="B17" t="n">
-        <v>79023</v>
+        <v>79053</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>377588</v>
+        <v>377206</v>
       </c>
       <c r="R17" t="n">
-        <v>6743996</v>
+        <v>6744255</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295134</v>
+        <v>127295117</v>
       </c>
       <c r="B18" t="n">
-        <v>79047</v>
+        <v>79029</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377206</v>
+        <v>377588</v>
       </c>
       <c r="R18" t="n">
-        <v>6744255</v>
+        <v>6743996</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2343,7 +2343,7 @@
         <v>127295152</v>
       </c>
       <c r="B19" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295126</v>
+        <v>127295140</v>
       </c>
       <c r="B22" t="n">
-        <v>96711</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377213</v>
+        <v>377379</v>
       </c>
       <c r="R22" t="n">
-        <v>6744163</v>
+        <v>6744330</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295162</v>
+        <v>127295106</v>
       </c>
       <c r="B23" t="n">
-        <v>78690</v>
+        <v>78788</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377576</v>
+        <v>377535</v>
       </c>
       <c r="R23" t="n">
-        <v>6744414</v>
+        <v>6744318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2829,7 +2829,7 @@
         <v>127295160</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295140</v>
+        <v>127295126</v>
       </c>
       <c r="B25" t="n">
-        <v>79023</v>
+        <v>96719</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377379</v>
+        <v>377213</v>
       </c>
       <c r="R25" t="n">
-        <v>6744330</v>
+        <v>6744163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295106</v>
+        <v>127295162</v>
       </c>
       <c r="B26" t="n">
-        <v>78782</v>
+        <v>78696</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377535</v>
+        <v>377576</v>
       </c>
       <c r="R26" t="n">
-        <v>6744318</v>
+        <v>6744414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
         <v>127295115</v>
       </c>
       <c r="B27" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295118</v>
+        <v>127295164</v>
       </c>
       <c r="B28" t="n">
-        <v>78782</v>
+        <v>79061</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377523</v>
+        <v>377671</v>
       </c>
       <c r="R28" t="n">
-        <v>6744132</v>
+        <v>6744350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295164</v>
+        <v>127295118</v>
       </c>
       <c r="B29" t="n">
-        <v>79055</v>
+        <v>78788</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377671</v>
+        <v>377523</v>
       </c>
       <c r="R29" t="n">
-        <v>6744350</v>
+        <v>6744132</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
         <v>127295100</v>
       </c>
       <c r="B30" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295158</v>
+        <v>127295138</v>
       </c>
       <c r="B31" t="n">
-        <v>79023</v>
+        <v>79061</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377488</v>
+        <v>377211</v>
       </c>
       <c r="R31" t="n">
-        <v>6744404</v>
+        <v>6744196</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295165</v>
+        <v>127295105</v>
       </c>
       <c r="B32" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377640</v>
+        <v>377468</v>
       </c>
       <c r="R32" t="n">
-        <v>6744349</v>
+        <v>6744527</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295138</v>
+        <v>127295116</v>
       </c>
       <c r="B33" t="n">
-        <v>79055</v>
+        <v>79618</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377211</v>
+        <v>377494</v>
       </c>
       <c r="R33" t="n">
-        <v>6744196</v>
+        <v>6744143</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295116</v>
+        <v>127295158</v>
       </c>
       <c r="B34" t="n">
-        <v>79612</v>
+        <v>79029</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377494</v>
+        <v>377488</v>
       </c>
       <c r="R34" t="n">
-        <v>6744143</v>
+        <v>6744404</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295105</v>
+        <v>127295165</v>
       </c>
       <c r="B35" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377468</v>
+        <v>377640</v>
       </c>
       <c r="R35" t="n">
-        <v>6744527</v>
+        <v>6744349</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295108</v>
+        <v>127295151</v>
       </c>
       <c r="B36" t="n">
-        <v>78782</v>
+        <v>79029</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>377545</v>
+        <v>377506</v>
       </c>
       <c r="R36" t="n">
-        <v>6744314</v>
+        <v>6744399</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4090,7 +4090,7 @@
         <v>127295109</v>
       </c>
       <c r="B37" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4184,10 +4184,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295151</v>
+        <v>127295108</v>
       </c>
       <c r="B38" t="n">
-        <v>79023</v>
+        <v>78788</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4195,21 +4195,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4219,10 +4219,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>377506</v>
+        <v>377545</v>
       </c>
       <c r="R38" t="n">
-        <v>6744399</v>
+        <v>6744314</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4284,7 +4284,7 @@
         <v>127295128</v>
       </c>
       <c r="B39" t="n">
-        <v>79055</v>
+        <v>79061</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4381,7 +4381,7 @@
         <v>127295129</v>
       </c>
       <c r="B40" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4478,7 +4478,7 @@
         <v>127295142</v>
       </c>
       <c r="B41" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4575,7 +4575,7 @@
         <v>127295135</v>
       </c>
       <c r="B42" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4672,7 +4672,7 @@
         <v>127295107</v>
       </c>
       <c r="B43" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B44" t="n">
-        <v>78782</v>
+        <v>78787</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R44" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B45" t="n">
-        <v>78781</v>
+        <v>78788</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R45" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4963,7 +4963,7 @@
         <v>127295132</v>
       </c>
       <c r="B46" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>127295121</v>
       </c>
       <c r="B47" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295143</v>
+        <v>127295111</v>
       </c>
       <c r="B48" t="n">
-        <v>78690</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377379</v>
+        <v>377466</v>
       </c>
       <c r="R48" t="n">
-        <v>6744326</v>
+        <v>6744500</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295111</v>
+        <v>127295167</v>
       </c>
       <c r="B49" t="n">
-        <v>79023</v>
+        <v>79647</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377466</v>
+        <v>377647</v>
       </c>
       <c r="R49" t="n">
-        <v>6744500</v>
+        <v>6744358</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5330,6 +5330,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5348,10 +5349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295167</v>
+        <v>127295143</v>
       </c>
       <c r="B50" t="n">
-        <v>79641</v>
+        <v>78696</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5359,21 +5360,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5383,10 +5384,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377647</v>
+        <v>377379</v>
       </c>
       <c r="R50" t="n">
-        <v>6744358</v>
+        <v>6744326</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5427,7 +5428,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -1661,10 +1661,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295136</v>
+        <v>127295147</v>
       </c>
       <c r="B12" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,21 +1672,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1696,10 +1696,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377216</v>
+        <v>377575</v>
       </c>
       <c r="R12" t="n">
-        <v>6744274</v>
+        <v>6744364</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1758,7 +1758,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295147</v>
+        <v>127295101</v>
       </c>
       <c r="B13" t="n">
         <v>79647</v>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377575</v>
+        <v>377493</v>
       </c>
       <c r="R13" t="n">
-        <v>6744364</v>
+        <v>6744550</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295101</v>
+        <v>127295136</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377493</v>
+        <v>377216</v>
       </c>
       <c r="R15" t="n">
-        <v>6744550</v>
+        <v>6744274</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295140</v>
+        <v>127295126</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>96720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377379</v>
+        <v>377213</v>
       </c>
       <c r="R22" t="n">
-        <v>6744330</v>
+        <v>6744163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295106</v>
+        <v>127295162</v>
       </c>
       <c r="B23" t="n">
-        <v>78788</v>
+        <v>78696</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377535</v>
+        <v>377576</v>
       </c>
       <c r="R23" t="n">
-        <v>6744318</v>
+        <v>6744414</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295160</v>
+        <v>127295106</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377463</v>
+        <v>377535</v>
       </c>
       <c r="R24" t="n">
-        <v>6744378</v>
+        <v>6744318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295126</v>
+        <v>127295160</v>
       </c>
       <c r="B25" t="n">
-        <v>96719</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377213</v>
+        <v>377463</v>
       </c>
       <c r="R25" t="n">
-        <v>6744163</v>
+        <v>6744378</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295162</v>
+        <v>127295140</v>
       </c>
       <c r="B26" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377576</v>
+        <v>377379</v>
       </c>
       <c r="R26" t="n">
-        <v>6744414</v>
+        <v>6744330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295164</v>
+        <v>127295118</v>
       </c>
       <c r="B28" t="n">
-        <v>79061</v>
+        <v>78788</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377671</v>
+        <v>377523</v>
       </c>
       <c r="R28" t="n">
-        <v>6744350</v>
+        <v>6744132</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295118</v>
+        <v>127295164</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>79061</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377523</v>
+        <v>377671</v>
       </c>
       <c r="R29" t="n">
-        <v>6744132</v>
+        <v>6744350</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295100</v>
+        <v>127295158</v>
       </c>
       <c r="B30" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377499</v>
+        <v>377488</v>
       </c>
       <c r="R30" t="n">
-        <v>6744545</v>
+        <v>6744404</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295138</v>
+        <v>127295165</v>
       </c>
       <c r="B31" t="n">
-        <v>79061</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377211</v>
+        <v>377640</v>
       </c>
       <c r="R31" t="n">
-        <v>6744196</v>
+        <v>6744349</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295105</v>
+        <v>127295116</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>79618</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377468</v>
+        <v>377494</v>
       </c>
       <c r="R32" t="n">
-        <v>6744527</v>
+        <v>6744143</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295116</v>
+        <v>127295100</v>
       </c>
       <c r="B33" t="n">
-        <v>79618</v>
+        <v>78787</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377494</v>
+        <v>377499</v>
       </c>
       <c r="R33" t="n">
-        <v>6744143</v>
+        <v>6744545</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295158</v>
+        <v>127295138</v>
       </c>
       <c r="B34" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377488</v>
+        <v>377211</v>
       </c>
       <c r="R34" t="n">
-        <v>6744404</v>
+        <v>6744196</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295165</v>
+        <v>127295105</v>
       </c>
       <c r="B35" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377640</v>
+        <v>377468</v>
       </c>
       <c r="R35" t="n">
-        <v>6744349</v>
+        <v>6744527</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,10 +3990,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295151</v>
+        <v>127295109</v>
       </c>
       <c r="B36" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4001,21 +4001,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>377506</v>
+        <v>377479</v>
       </c>
       <c r="R36" t="n">
-        <v>6744399</v>
+        <v>6744536</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4087,10 +4087,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295109</v>
+        <v>127295151</v>
       </c>
       <c r="B37" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4098,21 +4098,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4122,10 +4122,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>377479</v>
+        <v>377506</v>
       </c>
       <c r="R37" t="n">
-        <v>6744536</v>
+        <v>6744399</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B39" t="n">
-        <v>79061</v>
+        <v>78788</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R39" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>79061</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R40" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B44" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R44" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R45" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295132</v>
+        <v>127295121</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4971,21 +4971,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>377208</v>
+        <v>377523</v>
       </c>
       <c r="R46" t="n">
-        <v>6744241</v>
+        <v>6744136</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295121</v>
+        <v>127295132</v>
       </c>
       <c r="B47" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>377523</v>
+        <v>377208</v>
       </c>
       <c r="R47" t="n">
-        <v>6744136</v>
+        <v>6744241</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295111</v>
+        <v>127295167</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377466</v>
+        <v>377647</v>
       </c>
       <c r="R48" t="n">
-        <v>6744500</v>
+        <v>6744358</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5233,6 +5233,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5251,10 +5252,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295167</v>
+        <v>127295143</v>
       </c>
       <c r="B49" t="n">
-        <v>79647</v>
+        <v>78696</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5262,21 +5263,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5286,10 +5287,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377647</v>
+        <v>377379</v>
       </c>
       <c r="R49" t="n">
-        <v>6744358</v>
+        <v>6744326</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5330,7 +5331,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5349,10 +5349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295143</v>
+        <v>127295111</v>
       </c>
       <c r="B50" t="n">
-        <v>78696</v>
+        <v>79029</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377379</v>
+        <v>377466</v>
       </c>
       <c r="R50" t="n">
-        <v>6744326</v>
+        <v>6744500</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295133</v>
+        <v>127295154</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377237</v>
+        <v>377487</v>
       </c>
       <c r="R3" t="n">
-        <v>6744276</v>
+        <v>6744422</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,6 +866,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -884,10 +885,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295154</v>
+        <v>127295133</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +896,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377487</v>
+        <v>377237</v>
       </c>
       <c r="R4" t="n">
-        <v>6744422</v>
+        <v>6744276</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,7 +964,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295150</v>
+        <v>127295145</v>
       </c>
       <c r="B8" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377507</v>
+        <v>377331</v>
       </c>
       <c r="R8" t="n">
-        <v>6744400</v>
+        <v>6744278</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295145</v>
+        <v>127295150</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377331</v>
+        <v>377507</v>
       </c>
       <c r="R9" t="n">
-        <v>6744278</v>
+        <v>6744400</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295101</v>
+        <v>127295136</v>
       </c>
       <c r="B13" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,21 +1769,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377493</v>
+        <v>377216</v>
       </c>
       <c r="R13" t="n">
-        <v>6744550</v>
+        <v>6744274</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1855,7 +1855,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295114</v>
+        <v>127295101</v>
       </c>
       <c r="B14" t="n">
         <v>79647</v>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377455</v>
+        <v>377493</v>
       </c>
       <c r="R14" t="n">
-        <v>6744199</v>
+        <v>6744550</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1952,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295136</v>
+        <v>127295114</v>
       </c>
       <c r="B15" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1963,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1987,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377216</v>
+        <v>377455</v>
       </c>
       <c r="R15" t="n">
-        <v>6744274</v>
+        <v>6744199</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,32 +2146,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295134</v>
+        <v>127295117</v>
       </c>
       <c r="B17" t="n">
-        <v>79053</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>377206</v>
+        <v>377588</v>
       </c>
       <c r="R17" t="n">
-        <v>6744255</v>
+        <v>6743996</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2243,32 +2243,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295117</v>
+        <v>127295134</v>
       </c>
       <c r="B18" t="n">
-        <v>79029</v>
+        <v>79053</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2278,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377588</v>
+        <v>377206</v>
       </c>
       <c r="R18" t="n">
-        <v>6743996</v>
+        <v>6744255</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B20" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295126</v>
+        <v>127295106</v>
       </c>
       <c r="B22" t="n">
-        <v>96720</v>
+        <v>78788</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377213</v>
+        <v>377535</v>
       </c>
       <c r="R22" t="n">
-        <v>6744163</v>
+        <v>6744318</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295162</v>
+        <v>127295126</v>
       </c>
       <c r="B23" t="n">
-        <v>78696</v>
+        <v>96720</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377576</v>
+        <v>377213</v>
       </c>
       <c r="R23" t="n">
-        <v>6744414</v>
+        <v>6744163</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295106</v>
+        <v>127295162</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>78696</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377535</v>
+        <v>377576</v>
       </c>
       <c r="R24" t="n">
-        <v>6744318</v>
+        <v>6744414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295118</v>
+        <v>127295164</v>
       </c>
       <c r="B28" t="n">
-        <v>78788</v>
+        <v>79061</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377523</v>
+        <v>377671</v>
       </c>
       <c r="R28" t="n">
-        <v>6744132</v>
+        <v>6744350</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295164</v>
+        <v>127295118</v>
       </c>
       <c r="B29" t="n">
-        <v>79061</v>
+        <v>78788</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377671</v>
+        <v>377523</v>
       </c>
       <c r="R29" t="n">
-        <v>6744350</v>
+        <v>6744132</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,10 +3408,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295158</v>
+        <v>127295138</v>
       </c>
       <c r="B30" t="n">
-        <v>79029</v>
+        <v>79061</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3419,21 +3419,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3443,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377488</v>
+        <v>377211</v>
       </c>
       <c r="R30" t="n">
-        <v>6744404</v>
+        <v>6744196</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295165</v>
+        <v>127295100</v>
       </c>
       <c r="B31" t="n">
-        <v>79029</v>
+        <v>78787</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377640</v>
+        <v>377499</v>
       </c>
       <c r="R31" t="n">
-        <v>6744349</v>
+        <v>6744545</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295116</v>
+        <v>127295158</v>
       </c>
       <c r="B32" t="n">
-        <v>79618</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377494</v>
+        <v>377488</v>
       </c>
       <c r="R32" t="n">
-        <v>6744143</v>
+        <v>6744404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295100</v>
+        <v>127295165</v>
       </c>
       <c r="B33" t="n">
-        <v>78787</v>
+        <v>79029</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377499</v>
+        <v>377640</v>
       </c>
       <c r="R33" t="n">
-        <v>6744545</v>
+        <v>6744349</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295138</v>
+        <v>127295116</v>
       </c>
       <c r="B34" t="n">
-        <v>79061</v>
+        <v>79618</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377211</v>
+        <v>377494</v>
       </c>
       <c r="R34" t="n">
-        <v>6744196</v>
+        <v>6744143</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B39" t="n">
-        <v>78788</v>
+        <v>79061</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R39" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B40" t="n">
-        <v>79061</v>
+        <v>78788</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R40" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R44" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B45" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R45" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4960,10 +4960,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295121</v>
+        <v>127295132</v>
       </c>
       <c r="B46" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4971,21 +4971,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>377523</v>
+        <v>377208</v>
       </c>
       <c r="R46" t="n">
-        <v>6744136</v>
+        <v>6744241</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295132</v>
+        <v>127295121</v>
       </c>
       <c r="B47" t="n">
-        <v>79029</v>
+        <v>79647</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5068,21 +5068,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5092,10 +5092,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>377208</v>
+        <v>377523</v>
       </c>
       <c r="R47" t="n">
-        <v>6744241</v>
+        <v>6744136</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295167</v>
+        <v>127295111</v>
       </c>
       <c r="B48" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377647</v>
+        <v>377466</v>
       </c>
       <c r="R48" t="n">
-        <v>6744358</v>
+        <v>6744500</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5233,7 +5233,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5252,10 +5251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295143</v>
+        <v>127295167</v>
       </c>
       <c r="B49" t="n">
-        <v>78696</v>
+        <v>79647</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5263,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5287,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377379</v>
+        <v>377647</v>
       </c>
       <c r="R49" t="n">
-        <v>6744326</v>
+        <v>6744358</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5331,6 +5330,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5349,10 +5349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295111</v>
+        <v>127295143</v>
       </c>
       <c r="B50" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5360,21 +5360,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5384,10 +5384,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377466</v>
+        <v>377379</v>
       </c>
       <c r="R50" t="n">
-        <v>6744500</v>
+        <v>6744326</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -2438,10 +2438,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295113</v>
+        <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2449,21 +2449,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2535,10 +2535,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295112</v>
+        <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2546,21 +2546,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295106</v>
+        <v>127295160</v>
       </c>
       <c r="B22" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377535</v>
+        <v>377463</v>
       </c>
       <c r="R22" t="n">
-        <v>6744318</v>
+        <v>6744378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295126</v>
+        <v>127295140</v>
       </c>
       <c r="B23" t="n">
-        <v>96720</v>
+        <v>79029</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377213</v>
+        <v>377379</v>
       </c>
       <c r="R23" t="n">
-        <v>6744163</v>
+        <v>6744330</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295162</v>
+        <v>127295106</v>
       </c>
       <c r="B24" t="n">
-        <v>78696</v>
+        <v>78788</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377576</v>
+        <v>377535</v>
       </c>
       <c r="R24" t="n">
-        <v>6744414</v>
+        <v>6744318</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295160</v>
+        <v>127295126</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>96721</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377463</v>
+        <v>377213</v>
       </c>
       <c r="R25" t="n">
-        <v>6744378</v>
+        <v>6744163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295140</v>
+        <v>127295162</v>
       </c>
       <c r="B26" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377379</v>
+        <v>377576</v>
       </c>
       <c r="R26" t="n">
-        <v>6744330</v>
+        <v>6744414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295115</v>
+        <v>127295164</v>
       </c>
       <c r="B27" t="n">
-        <v>79647</v>
+        <v>79061</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377494</v>
+        <v>377671</v>
       </c>
       <c r="R27" t="n">
-        <v>6744143</v>
+        <v>6744350</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,10 +3214,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295164</v>
+        <v>127295115</v>
       </c>
       <c r="B28" t="n">
-        <v>79061</v>
+        <v>79647</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3225,21 +3225,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377671</v>
+        <v>377494</v>
       </c>
       <c r="R28" t="n">
-        <v>6744350</v>
+        <v>6744143</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295142</v>
+        <v>127295107</v>
       </c>
       <c r="B41" t="n">
-        <v>79029</v>
+        <v>78788</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377328</v>
+        <v>377557</v>
       </c>
       <c r="R41" t="n">
-        <v>6744286</v>
+        <v>6744301</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295135</v>
+        <v>127295142</v>
       </c>
       <c r="B42" t="n">
         <v>79029</v>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>377206</v>
+        <v>377328</v>
       </c>
       <c r="R42" t="n">
-        <v>6744255</v>
+        <v>6744286</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4669,10 +4669,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295107</v>
+        <v>127295135</v>
       </c>
       <c r="B43" t="n">
-        <v>78788</v>
+        <v>79029</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4680,21 +4680,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4704,10 +4704,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>377557</v>
+        <v>377206</v>
       </c>
       <c r="R43" t="n">
-        <v>6744301</v>
+        <v>6744255</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4766,10 +4766,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295155</v>
+        <v>127295104</v>
       </c>
       <c r="B44" t="n">
-        <v>78787</v>
+        <v>78788</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4777,21 +4777,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4801,10 +4801,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377489</v>
+        <v>377491</v>
       </c>
       <c r="R44" t="n">
-        <v>6744396</v>
+        <v>6744551</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4863,10 +4863,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295104</v>
+        <v>127295155</v>
       </c>
       <c r="B45" t="n">
-        <v>78788</v>
+        <v>78787</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4874,21 +4874,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4898,10 +4898,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377491</v>
+        <v>377489</v>
       </c>
       <c r="R45" t="n">
-        <v>6744551</v>
+        <v>6744396</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295111</v>
+        <v>127295143</v>
       </c>
       <c r="B48" t="n">
-        <v>79029</v>
+        <v>78696</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377466</v>
+        <v>377379</v>
       </c>
       <c r="R48" t="n">
-        <v>6744500</v>
+        <v>6744326</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295167</v>
+        <v>127295111</v>
       </c>
       <c r="B49" t="n">
-        <v>79647</v>
+        <v>79029</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377647</v>
+        <v>377466</v>
       </c>
       <c r="R49" t="n">
-        <v>6744358</v>
+        <v>6744500</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5330,7 +5330,6 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5349,10 +5348,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295143</v>
+        <v>127295167</v>
       </c>
       <c r="B50" t="n">
-        <v>78696</v>
+        <v>79647</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5360,21 +5359,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5384,10 +5383,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377379</v>
+        <v>377647</v>
       </c>
       <c r="R50" t="n">
-        <v>6744326</v>
+        <v>6744358</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5428,6 +5427,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY50"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5444,6 +5444,2140 @@
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128360478</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>377443</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6744347</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128360489</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>377486</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6744532</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128360469</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>377179</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6744259</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128360480</v>
+      </c>
+      <c r="B54" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>377249</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6744297</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128360482</v>
+      </c>
+      <c r="B55" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>377306</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6744244</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128360475</v>
+      </c>
+      <c r="B56" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>377558</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6744145</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128360476</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>377558</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6744145</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128360467</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>377532</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6744383</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128360460</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>377453</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6744153</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128360449</v>
+      </c>
+      <c r="B60" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>377237</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6744295</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128360485</v>
+      </c>
+      <c r="B61" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>377332</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6744250</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128360464</v>
+      </c>
+      <c r="B62" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>377405</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6744360</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128360450</v>
+      </c>
+      <c r="B63" t="n">
+        <v>79063</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>185</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>377189</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6744221</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128360465</v>
+      </c>
+      <c r="B64" t="n">
+        <v>79063</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>185</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>377505</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6744610</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128360447</v>
+      </c>
+      <c r="B65" t="n">
+        <v>79649</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>377575</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6744372</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128360463</v>
+      </c>
+      <c r="B66" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>377620</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6744362</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128360487</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>377564</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6744311</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128360445</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>377247</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6744296</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128360488</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>377564</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6744311</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128360470</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79031</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>377452</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6744550</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128360454</v>
+      </c>
+      <c r="B71" t="n">
+        <v>78790</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>377483</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6744504</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128360453</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78789</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>377483</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6744504</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5449,7 +5449,7 @@
         <v>128360478</v>
       </c>
       <c r="B51" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>128360489</v>
       </c>
       <c r="B52" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>128360469</v>
       </c>
       <c r="B53" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>128360480</v>
       </c>
       <c r="B54" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360482</v>
+        <v>128360475</v>
       </c>
       <c r="B55" t="n">
         <v>78790</v>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R55" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360475</v>
+        <v>128360482</v>
       </c>
       <c r="B56" t="n">
-        <v>78789</v>
+        <v>78791</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377558</v>
+        <v>377306</v>
       </c>
       <c r="R56" t="n">
-        <v>6744145</v>
+        <v>6744244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360476</v>
+        <v>128360467</v>
       </c>
       <c r="B57" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377558</v>
+        <v>377532</v>
       </c>
       <c r="R57" t="n">
-        <v>6744145</v>
+        <v>6744383</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360467</v>
+        <v>128360460</v>
       </c>
       <c r="B58" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377532</v>
+        <v>377453</v>
       </c>
       <c r="R58" t="n">
-        <v>6744383</v>
+        <v>6744153</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360460</v>
+        <v>128360476</v>
       </c>
       <c r="B59" t="n">
-        <v>79031</v>
+        <v>78791</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377453</v>
+        <v>377558</v>
       </c>
       <c r="R59" t="n">
-        <v>6744153</v>
+        <v>6744145</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128360449</v>
+        <v>128360464</v>
       </c>
       <c r="B60" t="n">
-        <v>78790</v>
+        <v>79032</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6330,21 +6330,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>377237</v>
+        <v>377405</v>
       </c>
       <c r="R60" t="n">
-        <v>6744295</v>
+        <v>6744360</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6419,7 +6419,7 @@
         <v>128360485</v>
       </c>
       <c r="B61" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128360464</v>
+        <v>128360449</v>
       </c>
       <c r="B62" t="n">
-        <v>79031</v>
+        <v>78791</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>377405</v>
+        <v>377237</v>
       </c>
       <c r="R62" t="n">
-        <v>6744360</v>
+        <v>6744295</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360450</v>
+        <v>128360465</v>
       </c>
       <c r="B63" t="n">
-        <v>79063</v>
+        <v>79064</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377189</v>
+        <v>377505</v>
       </c>
       <c r="R63" t="n">
-        <v>6744221</v>
+        <v>6744610</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,10 +6707,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360465</v>
+        <v>128360450</v>
       </c>
       <c r="B64" t="n">
-        <v>79063</v>
+        <v>79064</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377505</v>
+        <v>377189</v>
       </c>
       <c r="R64" t="n">
-        <v>6744610</v>
+        <v>6744221</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6807,7 +6807,7 @@
         <v>128360447</v>
       </c>
       <c r="B65" t="n">
-        <v>79649</v>
+        <v>79650</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>128360463</v>
       </c>
       <c r="B66" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128360487</v>
       </c>
       <c r="B67" t="n">
-        <v>78789</v>
+        <v>78790</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128360445</v>
       </c>
       <c r="B68" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128360488</v>
       </c>
       <c r="B69" t="n">
-        <v>78790</v>
+        <v>78791</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>128360470</v>
       </c>
       <c r="B70" t="n">
-        <v>79031</v>
+        <v>79032</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360454</v>
+        <v>128360453</v>
       </c>
       <c r="B71" t="n">
         <v>78790</v>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360453</v>
+        <v>128360454</v>
       </c>
       <c r="B72" t="n">
-        <v>78789</v>
+        <v>78791</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -6028,7 +6028,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360467</v>
+        <v>128360460</v>
       </c>
       <c r="B57" t="n">
         <v>79032</v>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377532</v>
+        <v>377453</v>
       </c>
       <c r="R57" t="n">
-        <v>6744383</v>
+        <v>6744153</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360460</v>
+        <v>128360467</v>
       </c>
       <c r="B58" t="n">
         <v>79032</v>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377453</v>
+        <v>377532</v>
       </c>
       <c r="R58" t="n">
-        <v>6744153</v>
+        <v>6744383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5449,7 +5449,7 @@
         <v>128360478</v>
       </c>
       <c r="B51" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>128360489</v>
       </c>
       <c r="B52" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>128360469</v>
       </c>
       <c r="B53" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>128360480</v>
       </c>
       <c r="B54" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128360475</v>
       </c>
       <c r="B55" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>128360482</v>
       </c>
       <c r="B56" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
         <v>128360460</v>
       </c>
       <c r="B57" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6128,7 +6128,7 @@
         <v>128360467</v>
       </c>
       <c r="B58" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>128360476</v>
       </c>
       <c r="B59" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128360464</v>
       </c>
       <c r="B60" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128360485</v>
       </c>
       <c r="B61" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128360449</v>
       </c>
       <c r="B62" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128360465</v>
       </c>
       <c r="B63" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128360450</v>
       </c>
       <c r="B64" t="n">
-        <v>79064</v>
+        <v>79115</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>128360447</v>
       </c>
       <c r="B65" t="n">
-        <v>79650</v>
+        <v>79702</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>128360463</v>
       </c>
       <c r="B66" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128360487</v>
       </c>
       <c r="B67" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128360445</v>
       </c>
       <c r="B68" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128360488</v>
       </c>
       <c r="B69" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>128360470</v>
       </c>
       <c r="B70" t="n">
-        <v>79032</v>
+        <v>79083</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>128360453</v>
       </c>
       <c r="B71" t="n">
-        <v>78790</v>
+        <v>78840</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>128360454</v>
       </c>
       <c r="B72" t="n">
-        <v>78791</v>
+        <v>78841</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360467</v>
+        <v>128360476</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6136,21 +6136,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377532</v>
+        <v>377558</v>
       </c>
       <c r="R58" t="n">
-        <v>6744383</v>
+        <v>6744145</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360476</v>
+        <v>128360467</v>
       </c>
       <c r="B59" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377558</v>
+        <v>377532</v>
       </c>
       <c r="R59" t="n">
-        <v>6744145</v>
+        <v>6744383</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6319,7 +6319,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128360464</v>
+        <v>128360485</v>
       </c>
       <c r="B60" t="n">
         <v>79083</v>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>377405</v>
+        <v>377332</v>
       </c>
       <c r="R60" t="n">
-        <v>6744360</v>
+        <v>6744250</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128360485</v>
+        <v>128360464</v>
       </c>
       <c r="B61" t="n">
         <v>79083</v>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>377332</v>
+        <v>377405</v>
       </c>
       <c r="R61" t="n">
-        <v>6744250</v>
+        <v>6744360</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360465</v>
+        <v>128360447</v>
       </c>
       <c r="B63" t="n">
-        <v>79115</v>
+        <v>79702</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377505</v>
+        <v>377575</v>
       </c>
       <c r="R63" t="n">
-        <v>6744610</v>
+        <v>6744372</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360450</v>
+        <v>128360465</v>
       </c>
       <c r="B64" t="n">
         <v>79115</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377189</v>
+        <v>377505</v>
       </c>
       <c r="R64" t="n">
-        <v>6744221</v>
+        <v>6744610</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360447</v>
+        <v>128360450</v>
       </c>
       <c r="B65" t="n">
-        <v>79702</v>
+        <v>79115</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377575</v>
+        <v>377189</v>
       </c>
       <c r="R65" t="n">
-        <v>6744372</v>
+        <v>6744221</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5834,10 +5834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360475</v>
+        <v>128360482</v>
       </c>
       <c r="B55" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377558</v>
+        <v>377306</v>
       </c>
       <c r="R55" t="n">
-        <v>6744145</v>
+        <v>6744244</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360482</v>
+        <v>128360475</v>
       </c>
       <c r="B56" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R56" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360476</v>
+        <v>128360467</v>
       </c>
       <c r="B58" t="n">
-        <v>78841</v>
+        <v>79083</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6136,21 +6136,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377558</v>
+        <v>377532</v>
       </c>
       <c r="R58" t="n">
-        <v>6744145</v>
+        <v>6744383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360467</v>
+        <v>128360476</v>
       </c>
       <c r="B59" t="n">
-        <v>79083</v>
+        <v>78841</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377532</v>
+        <v>377558</v>
       </c>
       <c r="R59" t="n">
-        <v>6744383</v>
+        <v>6744145</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5834,10 +5834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360482</v>
+        <v>128360475</v>
       </c>
       <c r="B55" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R55" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360475</v>
+        <v>128360482</v>
       </c>
       <c r="B56" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377558</v>
+        <v>377306</v>
       </c>
       <c r="R56" t="n">
-        <v>6744145</v>
+        <v>6744244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360460</v>
+        <v>128360467</v>
       </c>
       <c r="B57" t="n">
         <v>79083</v>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377453</v>
+        <v>377532</v>
       </c>
       <c r="R57" t="n">
-        <v>6744153</v>
+        <v>6744383</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360467</v>
+        <v>128360460</v>
       </c>
       <c r="B58" t="n">
         <v>79083</v>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377532</v>
+        <v>377453</v>
       </c>
       <c r="R58" t="n">
-        <v>6744383</v>
+        <v>6744153</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360447</v>
+        <v>128360465</v>
       </c>
       <c r="B63" t="n">
-        <v>79702</v>
+        <v>79115</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377575</v>
+        <v>377505</v>
       </c>
       <c r="R63" t="n">
-        <v>6744372</v>
+        <v>6744610</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360465</v>
+        <v>128360450</v>
       </c>
       <c r="B64" t="n">
         <v>79115</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377505</v>
+        <v>377189</v>
       </c>
       <c r="R64" t="n">
-        <v>6744610</v>
+        <v>6744221</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360450</v>
+        <v>128360447</v>
       </c>
       <c r="B65" t="n">
-        <v>79115</v>
+        <v>79702</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377189</v>
+        <v>377575</v>
       </c>
       <c r="R65" t="n">
-        <v>6744221</v>
+        <v>6744372</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360453</v>
+        <v>128360454</v>
       </c>
       <c r="B71" t="n">
-        <v>78840</v>
+        <v>78841</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360454</v>
+        <v>128360453</v>
       </c>
       <c r="B72" t="n">
-        <v>78841</v>
+        <v>78840</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5449,7 +5449,7 @@
         <v>128360478</v>
       </c>
       <c r="B51" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>128360489</v>
       </c>
       <c r="B52" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>128360469</v>
       </c>
       <c r="B53" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>128360480</v>
       </c>
       <c r="B54" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128360475</v>
       </c>
       <c r="B55" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>128360482</v>
       </c>
       <c r="B56" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360467</v>
+        <v>128360460</v>
       </c>
       <c r="B57" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377532</v>
+        <v>377453</v>
       </c>
       <c r="R57" t="n">
-        <v>6744383</v>
+        <v>6744153</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360460</v>
+        <v>128360467</v>
       </c>
       <c r="B58" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377453</v>
+        <v>377532</v>
       </c>
       <c r="R58" t="n">
-        <v>6744153</v>
+        <v>6744383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6225,7 +6225,7 @@
         <v>128360476</v>
       </c>
       <c r="B59" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128360485</v>
       </c>
       <c r="B60" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128360464</v>
       </c>
       <c r="B61" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128360449</v>
       </c>
       <c r="B62" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360465</v>
+        <v>128360447</v>
       </c>
       <c r="B63" t="n">
-        <v>79115</v>
+        <v>79706</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377505</v>
+        <v>377575</v>
       </c>
       <c r="R63" t="n">
-        <v>6744610</v>
+        <v>6744372</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,10 +6707,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360450</v>
+        <v>128360465</v>
       </c>
       <c r="B64" t="n">
-        <v>79115</v>
+        <v>79119</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377189</v>
+        <v>377505</v>
       </c>
       <c r="R64" t="n">
-        <v>6744221</v>
+        <v>6744610</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360447</v>
+        <v>128360450</v>
       </c>
       <c r="B65" t="n">
-        <v>79702</v>
+        <v>79119</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377575</v>
+        <v>377189</v>
       </c>
       <c r="R65" t="n">
-        <v>6744372</v>
+        <v>6744221</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6904,7 +6904,7 @@
         <v>128360463</v>
       </c>
       <c r="B66" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128360487</v>
       </c>
       <c r="B67" t="n">
-        <v>78840</v>
+        <v>78844</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128360445</v>
       </c>
       <c r="B68" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128360488</v>
       </c>
       <c r="B69" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>128360470</v>
       </c>
       <c r="B70" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360454</v>
+        <v>128360453</v>
       </c>
       <c r="B71" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360453</v>
+        <v>128360454</v>
       </c>
       <c r="B72" t="n">
-        <v>78840</v>
+        <v>78845</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5449,7 +5449,7 @@
         <v>128360478</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>128360489</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>128360469</v>
       </c>
       <c r="B53" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>128360480</v>
       </c>
       <c r="B54" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128360475</v>
       </c>
       <c r="B55" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>128360482</v>
       </c>
       <c r="B56" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360460</v>
+        <v>128360476</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>78847</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377453</v>
+        <v>377558</v>
       </c>
       <c r="R57" t="n">
-        <v>6744153</v>
+        <v>6744145</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360467</v>
+        <v>128360460</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377532</v>
+        <v>377453</v>
       </c>
       <c r="R58" t="n">
-        <v>6744383</v>
+        <v>6744153</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360476</v>
+        <v>128360467</v>
       </c>
       <c r="B59" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377558</v>
+        <v>377532</v>
       </c>
       <c r="R59" t="n">
-        <v>6744145</v>
+        <v>6744383</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
         <v>128360485</v>
       </c>
       <c r="B60" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128360464</v>
       </c>
       <c r="B61" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128360449</v>
       </c>
       <c r="B62" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6613,7 +6613,7 @@
         <v>128360447</v>
       </c>
       <c r="B63" t="n">
-        <v>79706</v>
+        <v>79708</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128360465</v>
       </c>
       <c r="B64" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>128360450</v>
       </c>
       <c r="B65" t="n">
-        <v>79119</v>
+        <v>79121</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>128360463</v>
       </c>
       <c r="B66" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128360487</v>
       </c>
       <c r="B67" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128360445</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128360488</v>
       </c>
       <c r="B69" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>128360470</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>128360453</v>
       </c>
       <c r="B71" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>128360454</v>
       </c>
       <c r="B72" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5834,10 +5834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360475</v>
+        <v>128360482</v>
       </c>
       <c r="B55" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377558</v>
+        <v>377306</v>
       </c>
       <c r="R55" t="n">
-        <v>6744145</v>
+        <v>6744244</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360482</v>
+        <v>128360475</v>
       </c>
       <c r="B56" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R56" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360476</v>
+        <v>128360460</v>
       </c>
       <c r="B57" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377558</v>
+        <v>377453</v>
       </c>
       <c r="R57" t="n">
-        <v>6744145</v>
+        <v>6744153</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360460</v>
+        <v>128360467</v>
       </c>
       <c r="B58" t="n">
         <v>79089</v>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377453</v>
+        <v>377532</v>
       </c>
       <c r="R58" t="n">
-        <v>6744153</v>
+        <v>6744383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360467</v>
+        <v>128360476</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377532</v>
+        <v>377558</v>
       </c>
       <c r="R59" t="n">
-        <v>6744383</v>
+        <v>6744145</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5834,10 +5834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360482</v>
+        <v>128360475</v>
       </c>
       <c r="B55" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R55" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360475</v>
+        <v>128360482</v>
       </c>
       <c r="B56" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377558</v>
+        <v>377306</v>
       </c>
       <c r="R56" t="n">
-        <v>6744145</v>
+        <v>6744244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,7 +6028,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360460</v>
+        <v>128360467</v>
       </c>
       <c r="B57" t="n">
         <v>79089</v>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377453</v>
+        <v>377532</v>
       </c>
       <c r="R57" t="n">
-        <v>6744153</v>
+        <v>6744383</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360467</v>
+        <v>128360476</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6136,21 +6136,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377532</v>
+        <v>377558</v>
       </c>
       <c r="R58" t="n">
-        <v>6744383</v>
+        <v>6744145</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360476</v>
+        <v>128360460</v>
       </c>
       <c r="B59" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377558</v>
+        <v>377453</v>
       </c>
       <c r="R59" t="n">
-        <v>6744145</v>
+        <v>6744153</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360447</v>
+        <v>128360465</v>
       </c>
       <c r="B63" t="n">
-        <v>79708</v>
+        <v>79121</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377575</v>
+        <v>377505</v>
       </c>
       <c r="R63" t="n">
-        <v>6744372</v>
+        <v>6744610</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360465</v>
+        <v>128360450</v>
       </c>
       <c r="B64" t="n">
         <v>79121</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377505</v>
+        <v>377189</v>
       </c>
       <c r="R64" t="n">
-        <v>6744610</v>
+        <v>6744221</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360450</v>
+        <v>128360447</v>
       </c>
       <c r="B65" t="n">
-        <v>79121</v>
+        <v>79708</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377189</v>
+        <v>377575</v>
       </c>
       <c r="R65" t="n">
-        <v>6744221</v>
+        <v>6744372</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5834,10 +5834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360475</v>
+        <v>128360482</v>
       </c>
       <c r="B55" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377558</v>
+        <v>377306</v>
       </c>
       <c r="R55" t="n">
-        <v>6744145</v>
+        <v>6744244</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360482</v>
+        <v>128360475</v>
       </c>
       <c r="B56" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R56" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360476</v>
+        <v>128360460</v>
       </c>
       <c r="B58" t="n">
-        <v>78847</v>
+        <v>79089</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6136,21 +6136,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377558</v>
+        <v>377453</v>
       </c>
       <c r="R58" t="n">
-        <v>6744145</v>
+        <v>6744153</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360460</v>
+        <v>128360476</v>
       </c>
       <c r="B59" t="n">
-        <v>79089</v>
+        <v>78847</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377453</v>
+        <v>377558</v>
       </c>
       <c r="R59" t="n">
-        <v>6744153</v>
+        <v>6744145</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360453</v>
+        <v>128360454</v>
       </c>
       <c r="B71" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360454</v>
+        <v>128360453</v>
       </c>
       <c r="B72" t="n">
-        <v>78847</v>
+        <v>78846</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360465</v>
+        <v>128360447</v>
       </c>
       <c r="B63" t="n">
-        <v>79121</v>
+        <v>79708</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377505</v>
+        <v>377575</v>
       </c>
       <c r="R63" t="n">
-        <v>6744610</v>
+        <v>6744372</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360450</v>
+        <v>128360465</v>
       </c>
       <c r="B64" t="n">
         <v>79121</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377189</v>
+        <v>377505</v>
       </c>
       <c r="R64" t="n">
-        <v>6744221</v>
+        <v>6744610</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360447</v>
+        <v>128360450</v>
       </c>
       <c r="B65" t="n">
-        <v>79708</v>
+        <v>79121</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377575</v>
+        <v>377189</v>
       </c>
       <c r="R65" t="n">
-        <v>6744372</v>
+        <v>6744221</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5449,7 +5449,7 @@
         <v>128360478</v>
       </c>
       <c r="B51" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>128360489</v>
       </c>
       <c r="B52" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>128360469</v>
       </c>
       <c r="B53" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>128360480</v>
       </c>
       <c r="B54" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128360482</v>
       </c>
       <c r="B55" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>128360475</v>
       </c>
       <c r="B56" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360467</v>
+        <v>128360460</v>
       </c>
       <c r="B57" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377532</v>
+        <v>377453</v>
       </c>
       <c r="R57" t="n">
-        <v>6744383</v>
+        <v>6744153</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360460</v>
+        <v>128360467</v>
       </c>
       <c r="B58" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377453</v>
+        <v>377532</v>
       </c>
       <c r="R58" t="n">
-        <v>6744153</v>
+        <v>6744383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6225,7 +6225,7 @@
         <v>128360476</v>
       </c>
       <c r="B59" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6322,7 +6322,7 @@
         <v>128360485</v>
       </c>
       <c r="B60" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128360464</v>
+        <v>128360449</v>
       </c>
       <c r="B61" t="n">
-        <v>79089</v>
+        <v>78874</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6427,21 +6427,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>377405</v>
+        <v>377237</v>
       </c>
       <c r="R61" t="n">
-        <v>6744360</v>
+        <v>6744295</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128360449</v>
+        <v>128360464</v>
       </c>
       <c r="B62" t="n">
-        <v>78847</v>
+        <v>79116</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>377237</v>
+        <v>377405</v>
       </c>
       <c r="R62" t="n">
-        <v>6744295</v>
+        <v>6744360</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>128360447</v>
       </c>
       <c r="B63" t="n">
-        <v>79708</v>
+        <v>79735</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128360465</v>
       </c>
       <c r="B64" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>128360450</v>
       </c>
       <c r="B65" t="n">
-        <v>79121</v>
+        <v>79148</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>128360463</v>
       </c>
       <c r="B66" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128360487</v>
       </c>
       <c r="B67" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128360445</v>
       </c>
       <c r="B68" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128360488</v>
       </c>
       <c r="B69" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>128360470</v>
       </c>
       <c r="B70" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360454</v>
+        <v>128360453</v>
       </c>
       <c r="B71" t="n">
-        <v>78847</v>
+        <v>78873</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360453</v>
+        <v>128360454</v>
       </c>
       <c r="B72" t="n">
-        <v>78846</v>
+        <v>78874</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5834,10 +5834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360482</v>
+        <v>128360475</v>
       </c>
       <c r="B55" t="n">
-        <v>78874</v>
+        <v>78873</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R55" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360475</v>
+        <v>128360482</v>
       </c>
       <c r="B56" t="n">
-        <v>78873</v>
+        <v>78874</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377558</v>
+        <v>377306</v>
       </c>
       <c r="R56" t="n">
-        <v>6744145</v>
+        <v>6744244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360460</v>
+        <v>128360476</v>
       </c>
       <c r="B57" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377453</v>
+        <v>377558</v>
       </c>
       <c r="R57" t="n">
-        <v>6744153</v>
+        <v>6744145</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,7 +6125,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360467</v>
+        <v>128360460</v>
       </c>
       <c r="B58" t="n">
         <v>79116</v>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377532</v>
+        <v>377453</v>
       </c>
       <c r="R58" t="n">
-        <v>6744383</v>
+        <v>6744153</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360476</v>
+        <v>128360467</v>
       </c>
       <c r="B59" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377558</v>
+        <v>377532</v>
       </c>
       <c r="R59" t="n">
-        <v>6744145</v>
+        <v>6744383</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128360449</v>
+        <v>128360464</v>
       </c>
       <c r="B61" t="n">
-        <v>78874</v>
+        <v>79116</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6427,21 +6427,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>377237</v>
+        <v>377405</v>
       </c>
       <c r="R61" t="n">
-        <v>6744295</v>
+        <v>6744360</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128360464</v>
+        <v>128360449</v>
       </c>
       <c r="B62" t="n">
-        <v>79116</v>
+        <v>78874</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>377405</v>
+        <v>377237</v>
       </c>
       <c r="R62" t="n">
-        <v>6744360</v>
+        <v>6744295</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360447</v>
+        <v>128360465</v>
       </c>
       <c r="B63" t="n">
-        <v>79735</v>
+        <v>79148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377575</v>
+        <v>377505</v>
       </c>
       <c r="R63" t="n">
-        <v>6744372</v>
+        <v>6744610</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360465</v>
+        <v>128360450</v>
       </c>
       <c r="B64" t="n">
         <v>79148</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377505</v>
+        <v>377189</v>
       </c>
       <c r="R64" t="n">
-        <v>6744610</v>
+        <v>6744221</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360450</v>
+        <v>128360447</v>
       </c>
       <c r="B65" t="n">
-        <v>79148</v>
+        <v>79735</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377189</v>
+        <v>377575</v>
       </c>
       <c r="R65" t="n">
-        <v>6744221</v>
+        <v>6744372</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5449,7 +5449,7 @@
         <v>128360478</v>
       </c>
       <c r="B51" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>128360489</v>
       </c>
       <c r="B52" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>128360469</v>
       </c>
       <c r="B53" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>128360480</v>
       </c>
       <c r="B54" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5834,10 +5834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360475</v>
+        <v>128360482</v>
       </c>
       <c r="B55" t="n">
-        <v>78873</v>
+        <v>78878</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377558</v>
+        <v>377306</v>
       </c>
       <c r="R55" t="n">
-        <v>6744145</v>
+        <v>6744244</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360482</v>
+        <v>128360475</v>
       </c>
       <c r="B56" t="n">
-        <v>78874</v>
+        <v>78877</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R56" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360476</v>
+        <v>128360460</v>
       </c>
       <c r="B57" t="n">
-        <v>78874</v>
+        <v>79120</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377558</v>
+        <v>377453</v>
       </c>
       <c r="R57" t="n">
-        <v>6744145</v>
+        <v>6744153</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360460</v>
+        <v>128360467</v>
       </c>
       <c r="B58" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377453</v>
+        <v>377532</v>
       </c>
       <c r="R58" t="n">
-        <v>6744153</v>
+        <v>6744383</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360467</v>
+        <v>128360476</v>
       </c>
       <c r="B59" t="n">
-        <v>79116</v>
+        <v>78878</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377532</v>
+        <v>377558</v>
       </c>
       <c r="R59" t="n">
-        <v>6744383</v>
+        <v>6744145</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6322,7 +6322,7 @@
         <v>128360485</v>
       </c>
       <c r="B60" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6419,7 +6419,7 @@
         <v>128360464</v>
       </c>
       <c r="B61" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6516,7 +6516,7 @@
         <v>128360449</v>
       </c>
       <c r="B62" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360465</v>
+        <v>128360447</v>
       </c>
       <c r="B63" t="n">
-        <v>79148</v>
+        <v>79739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377505</v>
+        <v>377575</v>
       </c>
       <c r="R63" t="n">
-        <v>6744610</v>
+        <v>6744372</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,10 +6707,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360450</v>
+        <v>128360465</v>
       </c>
       <c r="B64" t="n">
-        <v>79148</v>
+        <v>79152</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377189</v>
+        <v>377505</v>
       </c>
       <c r="R64" t="n">
-        <v>6744221</v>
+        <v>6744610</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360447</v>
+        <v>128360450</v>
       </c>
       <c r="B65" t="n">
-        <v>79735</v>
+        <v>79152</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377575</v>
+        <v>377189</v>
       </c>
       <c r="R65" t="n">
-        <v>6744372</v>
+        <v>6744221</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6904,7 +6904,7 @@
         <v>128360463</v>
       </c>
       <c r="B66" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128360487</v>
       </c>
       <c r="B67" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128360445</v>
       </c>
       <c r="B68" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128360488</v>
       </c>
       <c r="B69" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>128360470</v>
       </c>
       <c r="B70" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7389,7 +7389,7 @@
         <v>128360453</v>
       </c>
       <c r="B71" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7486,7 +7486,7 @@
         <v>128360454</v>
       </c>
       <c r="B72" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5834,10 +5834,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360482</v>
+        <v>128360475</v>
       </c>
       <c r="B55" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5845,21 +5845,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5869,10 +5869,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R55" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5931,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360475</v>
+        <v>128360482</v>
       </c>
       <c r="B56" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5942,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5966,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377558</v>
+        <v>377306</v>
       </c>
       <c r="R56" t="n">
-        <v>6744145</v>
+        <v>6744244</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128360485</v>
+        <v>128360449</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6330,21 +6330,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>377332</v>
+        <v>377237</v>
       </c>
       <c r="R60" t="n">
-        <v>6744250</v>
+        <v>6744295</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128360464</v>
+        <v>128360485</v>
       </c>
       <c r="B61" t="n">
         <v>79120</v>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>377405</v>
+        <v>377332</v>
       </c>
       <c r="R61" t="n">
-        <v>6744360</v>
+        <v>6744250</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128360449</v>
+        <v>128360464</v>
       </c>
       <c r="B62" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>377237</v>
+        <v>377405</v>
       </c>
       <c r="R62" t="n">
-        <v>6744295</v>
+        <v>6744360</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360447</v>
+        <v>128360465</v>
       </c>
       <c r="B63" t="n">
-        <v>79739</v>
+        <v>79152</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377575</v>
+        <v>377505</v>
       </c>
       <c r="R63" t="n">
-        <v>6744372</v>
+        <v>6744610</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360465</v>
+        <v>128360450</v>
       </c>
       <c r="B64" t="n">
         <v>79152</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377505</v>
+        <v>377189</v>
       </c>
       <c r="R64" t="n">
-        <v>6744610</v>
+        <v>6744221</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360450</v>
+        <v>128360447</v>
       </c>
       <c r="B65" t="n">
-        <v>79152</v>
+        <v>79739</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377189</v>
+        <v>377575</v>
       </c>
       <c r="R65" t="n">
-        <v>6744221</v>
+        <v>6744372</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360453</v>
+        <v>128360454</v>
       </c>
       <c r="B71" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360454</v>
+        <v>128360453</v>
       </c>
       <c r="B72" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360465</v>
+        <v>128360447</v>
       </c>
       <c r="B63" t="n">
-        <v>79152</v>
+        <v>79739</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377505</v>
+        <v>377575</v>
       </c>
       <c r="R63" t="n">
-        <v>6744610</v>
+        <v>6744372</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360450</v>
+        <v>128360465</v>
       </c>
       <c r="B64" t="n">
         <v>79152</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377189</v>
+        <v>377505</v>
       </c>
       <c r="R64" t="n">
-        <v>6744221</v>
+        <v>6744610</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360447</v>
+        <v>128360450</v>
       </c>
       <c r="B65" t="n">
-        <v>79739</v>
+        <v>79152</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377575</v>
+        <v>377189</v>
       </c>
       <c r="R65" t="n">
-        <v>6744372</v>
+        <v>6744221</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -6028,10 +6028,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360460</v>
+        <v>128360476</v>
       </c>
       <c r="B57" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377453</v>
+        <v>377558</v>
       </c>
       <c r="R57" t="n">
-        <v>6744153</v>
+        <v>6744145</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,10 +6222,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360476</v>
+        <v>128360460</v>
       </c>
       <c r="B59" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,21 +6233,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377558</v>
+        <v>377453</v>
       </c>
       <c r="R59" t="n">
-        <v>6744145</v>
+        <v>6744153</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128360449</v>
+        <v>128360485</v>
       </c>
       <c r="B60" t="n">
-        <v>78878</v>
+        <v>79120</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6330,21 +6330,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>377237</v>
+        <v>377332</v>
       </c>
       <c r="R60" t="n">
-        <v>6744295</v>
+        <v>6744250</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6416,7 +6416,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128360485</v>
+        <v>128360464</v>
       </c>
       <c r="B61" t="n">
         <v>79120</v>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>377332</v>
+        <v>377405</v>
       </c>
       <c r="R61" t="n">
-        <v>6744250</v>
+        <v>6744360</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128360464</v>
+        <v>128360449</v>
       </c>
       <c r="B62" t="n">
-        <v>79120</v>
+        <v>78878</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>377405</v>
+        <v>377237</v>
       </c>
       <c r="R62" t="n">
-        <v>6744360</v>
+        <v>6744295</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6610,10 +6610,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360447</v>
+        <v>128360465</v>
       </c>
       <c r="B63" t="n">
-        <v>79739</v>
+        <v>79152</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,21 +6621,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6645,10 +6645,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377575</v>
+        <v>377505</v>
       </c>
       <c r="R63" t="n">
-        <v>6744372</v>
+        <v>6744610</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360465</v>
+        <v>128360450</v>
       </c>
       <c r="B64" t="n">
         <v>79152</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377505</v>
+        <v>377189</v>
       </c>
       <c r="R64" t="n">
-        <v>6744610</v>
+        <v>6744221</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6804,10 +6804,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360450</v>
+        <v>128360447</v>
       </c>
       <c r="B65" t="n">
-        <v>79152</v>
+        <v>79739</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6815,21 +6815,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6839,10 +6839,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>377189</v>
+        <v>377575</v>
       </c>
       <c r="R65" t="n">
-        <v>6744221</v>
+        <v>6744372</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360454</v>
+        <v>128360453</v>
       </c>
       <c r="B71" t="n">
-        <v>78878</v>
+        <v>78877</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360453</v>
+        <v>128360454</v>
       </c>
       <c r="B72" t="n">
-        <v>78877</v>
+        <v>78878</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -5449,7 +5449,7 @@
         <v>128360478</v>
       </c>
       <c r="B51" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>128360489</v>
       </c>
       <c r="B52" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,7 +5643,7 @@
         <v>128360469</v>
       </c>
       <c r="B53" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>128360480</v>
       </c>
       <c r="B54" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>128360475</v>
       </c>
       <c r="B55" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>128360482</v>
       </c>
       <c r="B56" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6028,10 +6028,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360476</v>
+        <v>128360467</v>
       </c>
       <c r="B57" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6039,21 +6039,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377558</v>
+        <v>377532</v>
       </c>
       <c r="R57" t="n">
-        <v>6744145</v>
+        <v>6744383</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,10 +6125,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360467</v>
+        <v>128360476</v>
       </c>
       <c r="B58" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6136,21 +6136,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6160,10 +6160,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377532</v>
+        <v>377558</v>
       </c>
       <c r="R58" t="n">
-        <v>6744383</v>
+        <v>6744145</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6225,7 +6225,7 @@
         <v>128360460</v>
       </c>
       <c r="B59" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6319,10 +6319,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128360485</v>
+        <v>128360449</v>
       </c>
       <c r="B60" t="n">
-        <v>79120</v>
+        <v>78882</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6330,21 +6330,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>377332</v>
+        <v>377237</v>
       </c>
       <c r="R60" t="n">
-        <v>6744250</v>
+        <v>6744295</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128360464</v>
+        <v>128360485</v>
       </c>
       <c r="B61" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6451,10 +6451,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>377405</v>
+        <v>377332</v>
       </c>
       <c r="R61" t="n">
-        <v>6744360</v>
+        <v>6744250</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6513,10 +6513,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128360449</v>
+        <v>128360464</v>
       </c>
       <c r="B62" t="n">
-        <v>78878</v>
+        <v>79124</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,21 +6524,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6548,10 +6548,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>377237</v>
+        <v>377405</v>
       </c>
       <c r="R62" t="n">
-        <v>6744295</v>
+        <v>6744360</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6613,7 +6613,7 @@
         <v>128360465</v>
       </c>
       <c r="B63" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         <v>128360450</v>
       </c>
       <c r="B64" t="n">
-        <v>79152</v>
+        <v>79156</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>128360447</v>
       </c>
       <c r="B65" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>128360463</v>
       </c>
       <c r="B66" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>128360487</v>
       </c>
       <c r="B67" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>128360445</v>
       </c>
       <c r="B68" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7195,7 +7195,7 @@
         <v>128360488</v>
       </c>
       <c r="B69" t="n">
-        <v>78878</v>
+        <v>78882</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>128360470</v>
       </c>
       <c r="B70" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360453</v>
+        <v>128360454</v>
       </c>
       <c r="B71" t="n">
-        <v>78877</v>
+        <v>78882</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360454</v>
+        <v>128360453</v>
       </c>
       <c r="B72" t="n">
-        <v>78878</v>
+        <v>78881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -6028,7 +6028,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360467</v>
+        <v>128360460</v>
       </c>
       <c r="B57" t="n">
         <v>79124</v>
@@ -6063,10 +6063,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377532</v>
+        <v>377453</v>
       </c>
       <c r="R57" t="n">
-        <v>6744383</v>
+        <v>6744153</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360460</v>
+        <v>128360467</v>
       </c>
       <c r="B59" t="n">
         <v>79124</v>
@@ -6257,10 +6257,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377453</v>
+        <v>377532</v>
       </c>
       <c r="R59" t="n">
-        <v>6744153</v>
+        <v>6744383</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7386,10 +7386,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360454</v>
+        <v>128360453</v>
       </c>
       <c r="B71" t="n">
-        <v>78882</v>
+        <v>78881</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7397,21 +7397,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7483,10 +7483,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360453</v>
+        <v>128360454</v>
       </c>
       <c r="B72" t="n">
-        <v>78881</v>
+        <v>78882</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7494,21 +7494,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295154</v>
+        <v>127295133</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377487</v>
+        <v>377237</v>
       </c>
       <c r="R3" t="n">
-        <v>6744422</v>
+        <v>6744276</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -866,7 +866,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295133</v>
+        <v>127295154</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377237</v>
+        <v>377487</v>
       </c>
       <c r="R4" t="n">
-        <v>6744276</v>
+        <v>6744422</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,6 +963,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -982,10 +982,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295130</v>
+        <v>127295156</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>78770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +993,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377203</v>
+        <v>377489</v>
       </c>
       <c r="R5" t="n">
-        <v>6744197</v>
+        <v>6744396</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295156</v>
+        <v>127295130</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377489</v>
+        <v>377203</v>
       </c>
       <c r="R6" t="n">
-        <v>6744396</v>
+        <v>6744197</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295119</v>
+        <v>127295161</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>78770</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1187,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377599</v>
+        <v>377576</v>
       </c>
       <c r="R7" t="n">
-        <v>6744109</v>
+        <v>6744414</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295145</v>
+        <v>127295119</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79629</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1284,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1308,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377331</v>
+        <v>377599</v>
       </c>
       <c r="R8" t="n">
-        <v>6744278</v>
+        <v>6744109</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1370,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295150</v>
+        <v>127295145</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>79011</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1381,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377507</v>
+        <v>377331</v>
       </c>
       <c r="R9" t="n">
-        <v>6744400</v>
+        <v>6744278</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295163</v>
+        <v>127295150</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79629</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377441</v>
+        <v>377507</v>
       </c>
       <c r="R10" t="n">
-        <v>6744357</v>
+        <v>6744400</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1564,10 +1564,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295161</v>
+        <v>127295163</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,21 +1575,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1599,10 +1599,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377576</v>
+        <v>377441</v>
       </c>
       <c r="R11" t="n">
-        <v>6744414</v>
+        <v>6744357</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
         <v>127295147</v>
       </c>
       <c r="B12" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1761,7 +1761,7 @@
         <v>127295136</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1858,7 +1858,7 @@
         <v>127295101</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>127295114</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>127295144</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2149,7 +2149,7 @@
         <v>127295117</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2246,7 +2246,7 @@
         <v>127295134</v>
       </c>
       <c r="B18" t="n">
-        <v>79053</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2343,7 +2343,7 @@
         <v>127295152</v>
       </c>
       <c r="B19" t="n">
-        <v>78787</v>
+        <v>78769</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         <v>127295112</v>
       </c>
       <c r="B20" t="n">
-        <v>78787</v>
+        <v>78769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,7 +2538,7 @@
         <v>127295113</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2632,10 +2632,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295160</v>
+        <v>127295126</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>96689</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2643,21 +2643,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377463</v>
+        <v>377213</v>
       </c>
       <c r="R22" t="n">
-        <v>6744378</v>
+        <v>6744163</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,10 +2729,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295140</v>
+        <v>127295106</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>78770</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2740,21 +2740,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2764,10 +2764,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377379</v>
+        <v>377535</v>
       </c>
       <c r="R23" t="n">
-        <v>6744330</v>
+        <v>6744318</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,10 +2826,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295106</v>
+        <v>127295162</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>78678</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2837,21 +2837,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2861,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377535</v>
+        <v>377576</v>
       </c>
       <c r="R24" t="n">
-        <v>6744318</v>
+        <v>6744414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295126</v>
+        <v>127295160</v>
       </c>
       <c r="B25" t="n">
-        <v>96721</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2934,21 +2934,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377213</v>
+        <v>377463</v>
       </c>
       <c r="R25" t="n">
-        <v>6744163</v>
+        <v>6744378</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,10 +3020,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295162</v>
+        <v>127295140</v>
       </c>
       <c r="B26" t="n">
-        <v>78696</v>
+        <v>79011</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3031,21 +3031,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377576</v>
+        <v>377379</v>
       </c>
       <c r="R26" t="n">
-        <v>6744414</v>
+        <v>6744330</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,10 +3117,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295164</v>
+        <v>127295118</v>
       </c>
       <c r="B27" t="n">
-        <v>79061</v>
+        <v>78770</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3128,21 +3128,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3152,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377671</v>
+        <v>377523</v>
       </c>
       <c r="R27" t="n">
-        <v>6744350</v>
+        <v>6744132</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3217,7 +3217,7 @@
         <v>127295115</v>
       </c>
       <c r="B28" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,10 +3311,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295118</v>
+        <v>127295164</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3322,21 +3322,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377523</v>
+        <v>377671</v>
       </c>
       <c r="R29" t="n">
-        <v>6744132</v>
+        <v>6744350</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3411,7 +3411,7 @@
         <v>127295138</v>
       </c>
       <c r="B30" t="n">
-        <v>79061</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,10 +3505,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295100</v>
+        <v>127295116</v>
       </c>
       <c r="B31" t="n">
-        <v>78787</v>
+        <v>79600</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3516,21 +3516,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3540,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377499</v>
+        <v>377494</v>
       </c>
       <c r="R31" t="n">
-        <v>6744545</v>
+        <v>6744143</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,10 +3602,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295158</v>
+        <v>127295105</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>78770</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3613,21 +3613,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3637,10 +3637,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377488</v>
+        <v>377468</v>
       </c>
       <c r="R32" t="n">
-        <v>6744404</v>
+        <v>6744527</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,10 +3699,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295165</v>
+        <v>127295100</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>78769</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3710,21 +3710,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3734,10 +3734,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377640</v>
+        <v>377499</v>
       </c>
       <c r="R33" t="n">
-        <v>6744349</v>
+        <v>6744545</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,10 +3796,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295116</v>
+        <v>127295158</v>
       </c>
       <c r="B34" t="n">
-        <v>79618</v>
+        <v>79011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3807,21 +3807,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377494</v>
+        <v>377488</v>
       </c>
       <c r="R34" t="n">
-        <v>6744143</v>
+        <v>6744404</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295105</v>
+        <v>127295165</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,21 +3904,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377468</v>
+        <v>377640</v>
       </c>
       <c r="R35" t="n">
-        <v>6744527</v>
+        <v>6744349</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3993,7 +3993,7 @@
         <v>127295109</v>
       </c>
       <c r="B36" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>127295151</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,7 +4187,7 @@
         <v>127295108</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4281,10 +4281,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295128</v>
+        <v>127295129</v>
       </c>
       <c r="B39" t="n">
-        <v>79061</v>
+        <v>78770</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377209</v>
+        <v>377236</v>
       </c>
       <c r="R39" t="n">
-        <v>6744182</v>
+        <v>6744248</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,10 +4378,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295129</v>
+        <v>127295128</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4389,21 +4389,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377236</v>
+        <v>377209</v>
       </c>
       <c r="R40" t="n">
-        <v>6744248</v>
+        <v>6744182</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4475,10 +4475,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295107</v>
+        <v>127295142</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4486,21 +4486,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4510,10 +4510,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377557</v>
+        <v>377328</v>
       </c>
       <c r="R41" t="n">
-        <v>6744301</v>
+        <v>6744286</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295142</v>
+        <v>127295107</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>78770</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4583,21 +4583,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4607,10 +4607,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>377328</v>
+        <v>377557</v>
       </c>
       <c r="R42" t="n">
-        <v>6744286</v>
+        <v>6744301</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4672,7 +4672,7 @@
         <v>127295135</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>127295104</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4866,7 +4866,7 @@
         <v>127295155</v>
       </c>
       <c r="B45" t="n">
-        <v>78787</v>
+        <v>78769</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4963,7 +4963,7 @@
         <v>127295132</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>127295121</v>
       </c>
       <c r="B47" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5154,10 +5154,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295143</v>
+        <v>127295111</v>
       </c>
       <c r="B48" t="n">
-        <v>78696</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5165,21 +5165,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5189,10 +5189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377379</v>
+        <v>377466</v>
       </c>
       <c r="R48" t="n">
-        <v>6744326</v>
+        <v>6744500</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5251,10 +5251,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295111</v>
+        <v>127295167</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79629</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5286,10 +5286,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377466</v>
+        <v>377647</v>
       </c>
       <c r="R49" t="n">
-        <v>6744500</v>
+        <v>6744358</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5330,6 +5330,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5348,10 +5349,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295167</v>
+        <v>127295143</v>
       </c>
       <c r="B50" t="n">
-        <v>79647</v>
+        <v>78678</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5359,21 +5360,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5383,10 +5384,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377647</v>
+        <v>377379</v>
       </c>
       <c r="R50" t="n">
-        <v>6744358</v>
+        <v>6744326</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5427,7 +5428,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74111086</v>
+        <v>127295126</v>
       </c>
       <c r="B2" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1962</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mellanmyren, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>377581.7718514246</v>
+        <v>377213</v>
       </c>
       <c r="R2" t="n">
-        <v>6744308.058776441</v>
+        <v>6744163</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-11-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>anders tedeholm</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127295154</v>
+        <v>110083903</v>
       </c>
       <c r="B3" t="n">
-        <v>78788</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>377487</v>
+        <v>377145</v>
       </c>
       <c r="R3" t="n">
-        <v>6744422</v>
+        <v>6744272</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -866,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127295133</v>
+        <v>127295127</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -896,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -920,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>377237</v>
+        <v>377142</v>
       </c>
       <c r="R4" t="n">
-        <v>6744276</v>
+        <v>6744157</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127295130</v>
+        <v>127295128</v>
       </c>
       <c r="B5" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -993,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1017,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>377203</v>
+        <v>377209</v>
       </c>
       <c r="R5" t="n">
-        <v>6744197</v>
+        <v>6744182</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127295156</v>
+        <v>127295138</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1090,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1114,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>377489</v>
+        <v>377211</v>
       </c>
       <c r="R6" t="n">
-        <v>6744396</v>
+        <v>6744196</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1176,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127295119</v>
+        <v>127295148</v>
       </c>
       <c r="B7" t="n">
-        <v>79647</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1187,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1211,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>377599</v>
+        <v>377417</v>
       </c>
       <c r="R7" t="n">
-        <v>6744109</v>
+        <v>6744349</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1273,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127295145</v>
+        <v>127295157</v>
       </c>
       <c r="B8" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1284,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1308,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>377331</v>
+        <v>377479</v>
       </c>
       <c r="R8" t="n">
-        <v>6744278</v>
+        <v>6744432</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1370,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127295150</v>
+        <v>127295164</v>
       </c>
       <c r="B9" t="n">
-        <v>79647</v>
+        <v>79359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1381,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1405,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>377507</v>
+        <v>377671</v>
       </c>
       <c r="R9" t="n">
-        <v>6744400</v>
+        <v>6744350</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1467,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127295163</v>
+        <v>128360450</v>
       </c>
       <c r="B10" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1478,34 +1462,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>377441</v>
+        <v>377189</v>
       </c>
       <c r="R10" t="n">
-        <v>6744357</v>
+        <v>6744221</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127295161</v>
+        <v>128360456</v>
       </c>
       <c r="B11" t="n">
-        <v>78788</v>
+        <v>79359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1575,34 +1559,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>377576</v>
+        <v>377422</v>
       </c>
       <c r="R11" t="n">
-        <v>6744414</v>
+        <v>6744340</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127295147</v>
+        <v>128360465</v>
       </c>
       <c r="B12" t="n">
-        <v>79647</v>
+        <v>79359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1672,34 +1656,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>377575</v>
+        <v>377505</v>
       </c>
       <c r="R12" t="n">
-        <v>6744364</v>
+        <v>6744610</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,22 +1730,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127295136</v>
+        <v>128360481</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1769,34 +1753,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>377216</v>
+        <v>377268</v>
       </c>
       <c r="R13" t="n">
-        <v>6744274</v>
+        <v>6744298</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127295101</v>
+        <v>127295143</v>
       </c>
       <c r="B14" t="n">
-        <v>79647</v>
+        <v>78993</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1866,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1890,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>377493</v>
+        <v>377379</v>
       </c>
       <c r="R14" t="n">
-        <v>6744550</v>
+        <v>6744326</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1952,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127295114</v>
+        <v>127295162</v>
       </c>
       <c r="B15" t="n">
-        <v>79647</v>
+        <v>78993</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1963,21 +1947,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1987,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>377455</v>
+        <v>377576</v>
       </c>
       <c r="R15" t="n">
-        <v>6744199</v>
+        <v>6744414</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2049,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127295144</v>
+        <v>127295139</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2060,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2084,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>377285</v>
+        <v>377272</v>
       </c>
       <c r="R16" t="n">
-        <v>6744289</v>
+        <v>6744296</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2146,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127295117</v>
+        <v>74111086</v>
       </c>
       <c r="B17" t="n">
-        <v>79029</v>
+        <v>90932</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2157,34 +2141,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Mellanmyren, Vrm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>377588</v>
+        <v>377582</v>
       </c>
       <c r="R17" t="n">
-        <v>6743996</v>
+        <v>6744308</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2211,12 +2195,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2018-11-08</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2231,44 +2215,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>anders tedeholm</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127295134</v>
+        <v>127295149</v>
       </c>
       <c r="B18" t="n">
-        <v>79053</v>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2278,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>377206</v>
+        <v>377436</v>
       </c>
       <c r="R18" t="n">
-        <v>6744255</v>
+        <v>6744355</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2340,45 +2324,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127295152</v>
+        <v>110083906</v>
       </c>
       <c r="B19" t="n">
-        <v>78787</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>377487</v>
+        <v>377131</v>
       </c>
       <c r="R19" t="n">
-        <v>6744422</v>
+        <v>6744260</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2405,12 +2389,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-06-18</t>
+          <t>2023-06-14</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,7 +2403,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2438,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127295112</v>
+        <v>127295102</v>
       </c>
       <c r="B20" t="n">
-        <v>78787</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2473,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>377452</v>
+        <v>377503</v>
       </c>
       <c r="R20" t="n">
-        <v>6744197</v>
+        <v>6744557</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2535,32 +2518,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127295113</v>
+        <v>127295103</v>
       </c>
       <c r="B21" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2570,10 +2553,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>377452</v>
+        <v>377478</v>
       </c>
       <c r="R21" t="n">
-        <v>6744197</v>
+        <v>6744613</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2632,14 +2615,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127295160</v>
+        <v>127295111</v>
       </c>
       <c r="B22" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2667,10 +2650,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>377463</v>
+        <v>377466</v>
       </c>
       <c r="R22" t="n">
-        <v>6744378</v>
+        <v>6744500</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2729,14 +2712,14 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127295140</v>
+        <v>127295117</v>
       </c>
       <c r="B23" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2764,10 +2747,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>377379</v>
+        <v>377588</v>
       </c>
       <c r="R23" t="n">
-        <v>6744330</v>
+        <v>6743996</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2826,32 +2809,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127295106</v>
+        <v>127295130</v>
       </c>
       <c r="B24" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2861,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>377535</v>
+        <v>377203</v>
       </c>
       <c r="R24" t="n">
-        <v>6744318</v>
+        <v>6744197</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2923,32 +2906,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127295126</v>
+        <v>127295131</v>
       </c>
       <c r="B25" t="n">
-        <v>96721</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2958,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>377213</v>
+        <v>377262</v>
       </c>
       <c r="R25" t="n">
-        <v>6744163</v>
+        <v>6744290</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3020,32 +3003,32 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127295162</v>
+        <v>127295132</v>
       </c>
       <c r="B26" t="n">
-        <v>78696</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3055,10 +3038,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>377576</v>
+        <v>377208</v>
       </c>
       <c r="R26" t="n">
-        <v>6744414</v>
+        <v>6744241</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3117,32 +3100,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127295164</v>
+        <v>127295133</v>
       </c>
       <c r="B27" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3152,10 +3135,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>377671</v>
+        <v>377237</v>
       </c>
       <c r="R27" t="n">
-        <v>6744350</v>
+        <v>6744276</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3214,32 +3197,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127295115</v>
+        <v>127295135</v>
       </c>
       <c r="B28" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3249,10 +3232,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>377494</v>
+        <v>377206</v>
       </c>
       <c r="R28" t="n">
-        <v>6744143</v>
+        <v>6744255</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3311,32 +3294,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127295118</v>
+        <v>127295136</v>
       </c>
       <c r="B29" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3346,10 +3329,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>377523</v>
+        <v>377216</v>
       </c>
       <c r="R29" t="n">
-        <v>6744132</v>
+        <v>6744274</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3408,32 +3391,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127295138</v>
+        <v>127295140</v>
       </c>
       <c r="B30" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3443,10 +3426,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>377211</v>
+        <v>377379</v>
       </c>
       <c r="R30" t="n">
-        <v>6744196</v>
+        <v>6744330</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3505,32 +3488,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127295100</v>
+        <v>127295142</v>
       </c>
       <c r="B31" t="n">
-        <v>78787</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3540,10 +3523,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>377499</v>
+        <v>377328</v>
       </c>
       <c r="R31" t="n">
-        <v>6744545</v>
+        <v>6744286</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3602,14 +3585,14 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127295158</v>
+        <v>127295144</v>
       </c>
       <c r="B32" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -3637,10 +3620,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>377488</v>
+        <v>377285</v>
       </c>
       <c r="R32" t="n">
-        <v>6744404</v>
+        <v>6744289</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3699,14 +3682,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127295165</v>
+        <v>127295145</v>
       </c>
       <c r="B33" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3734,10 +3717,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>377640</v>
+        <v>377331</v>
       </c>
       <c r="R33" t="n">
-        <v>6744349</v>
+        <v>6744278</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3796,32 +3779,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127295116</v>
+        <v>127295146</v>
       </c>
       <c r="B34" t="n">
-        <v>79618</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3831,10 +3814,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>377494</v>
+        <v>377439</v>
       </c>
       <c r="R34" t="n">
-        <v>6744143</v>
+        <v>6744323</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3893,32 +3876,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127295105</v>
+        <v>127295151</v>
       </c>
       <c r="B35" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3928,10 +3911,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>377468</v>
+        <v>377506</v>
       </c>
       <c r="R35" t="n">
-        <v>6744527</v>
+        <v>6744399</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3990,32 +3973,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127295109</v>
+        <v>127295158</v>
       </c>
       <c r="B36" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4025,10 +4008,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>377479</v>
+        <v>377488</v>
       </c>
       <c r="R36" t="n">
-        <v>6744536</v>
+        <v>6744404</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4087,14 +4070,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127295151</v>
+        <v>127295160</v>
       </c>
       <c r="B37" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4122,10 +4105,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>377506</v>
+        <v>377463</v>
       </c>
       <c r="R37" t="n">
-        <v>6744399</v>
+        <v>6744378</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4184,32 +4167,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127295108</v>
+        <v>127295163</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4219,10 +4202,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>377545</v>
+        <v>377441</v>
       </c>
       <c r="R38" t="n">
-        <v>6744314</v>
+        <v>6744357</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4281,32 +4264,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127295128</v>
+        <v>127295165</v>
       </c>
       <c r="B39" t="n">
-        <v>79061</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4316,10 +4299,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>377209</v>
+        <v>377640</v>
       </c>
       <c r="R39" t="n">
-        <v>6744182</v>
+        <v>6744349</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4378,45 +4361,45 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127295129</v>
+        <v>128360445</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>377236</v>
+        <v>377247</v>
       </c>
       <c r="R40" t="n">
-        <v>6744248</v>
+        <v>6744296</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,57 +4446,57 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127295107</v>
+        <v>128360460</v>
       </c>
       <c r="B41" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>377557</v>
+        <v>377453</v>
       </c>
       <c r="R41" t="n">
-        <v>6744301</v>
+        <v>6744153</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4560,26 +4543,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127295142</v>
+        <v>128360463</v>
       </c>
       <c r="B42" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4603,14 +4586,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>377328</v>
+        <v>377620</v>
       </c>
       <c r="R42" t="n">
-        <v>6744286</v>
+        <v>6744362</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4657,26 +4640,26 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127295135</v>
+        <v>128360464</v>
       </c>
       <c r="B43" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -4700,14 +4683,14 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>377206</v>
+        <v>377405</v>
       </c>
       <c r="R43" t="n">
-        <v>6744255</v>
+        <v>6744360</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4754,57 +4737,57 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127295104</v>
+        <v>128360467</v>
       </c>
       <c r="B44" t="n">
-        <v>78788</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>377491</v>
+        <v>377532</v>
       </c>
       <c r="R44" t="n">
-        <v>6744551</v>
+        <v>6744383</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4851,57 +4834,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127295155</v>
+        <v>128360469</v>
       </c>
       <c r="B45" t="n">
-        <v>78787</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>377489</v>
+        <v>377179</v>
       </c>
       <c r="R45" t="n">
-        <v>6744396</v>
+        <v>6744259</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4948,26 +4931,26 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127295132</v>
+        <v>128360470</v>
       </c>
       <c r="B46" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -4991,14 +4974,14 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>377208</v>
+        <v>377452</v>
       </c>
       <c r="R46" t="n">
-        <v>6744241</v>
+        <v>6744550</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5045,57 +5028,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127295121</v>
+        <v>128360478</v>
       </c>
       <c r="B47" t="n">
-        <v>79647</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>377523</v>
+        <v>377443</v>
       </c>
       <c r="R47" t="n">
-        <v>6744136</v>
+        <v>6744347</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5142,57 +5125,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127295143</v>
+        <v>128360485</v>
       </c>
       <c r="B48" t="n">
-        <v>78696</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>377379</v>
+        <v>377332</v>
       </c>
       <c r="R48" t="n">
-        <v>6744326</v>
+        <v>6744250</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5239,26 +5222,26 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127295111</v>
+        <v>128360489</v>
       </c>
       <c r="B49" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5282,14 +5265,14 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+          <t>Hedtjärnsberget, Vrm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>377466</v>
+        <v>377486</v>
       </c>
       <c r="R49" t="n">
-        <v>6744500</v>
+        <v>6744532</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5336,44 +5319,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Helena Malmestrand</t>
+          <t>Dick Östberg</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127295167</v>
+        <v>127295134</v>
       </c>
       <c r="B50" t="n">
-        <v>79647</v>
+        <v>79351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>6434</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5383,10 +5366,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>377647</v>
+        <v>377206</v>
       </c>
       <c r="R50" t="n">
-        <v>6744358</v>
+        <v>6744255</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5427,7 +5410,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5446,10 +5428,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128360478</v>
+        <v>127295100</v>
       </c>
       <c r="B51" t="n">
-        <v>79124</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5457,34 +5439,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>377443</v>
+        <v>377499</v>
       </c>
       <c r="R51" t="n">
-        <v>6744347</v>
+        <v>6744545</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5531,22 +5513,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128360489</v>
+        <v>127295112</v>
       </c>
       <c r="B52" t="n">
-        <v>79124</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5554,34 +5536,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>377486</v>
+        <v>377452</v>
       </c>
       <c r="R52" t="n">
-        <v>6744532</v>
+        <v>6744197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5628,22 +5610,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128360469</v>
+        <v>127295152</v>
       </c>
       <c r="B53" t="n">
-        <v>79124</v>
+        <v>79084</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5651,34 +5633,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>377179</v>
+        <v>377487</v>
       </c>
       <c r="R53" t="n">
-        <v>6744259</v>
+        <v>6744422</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5719,28 +5701,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128360480</v>
+        <v>127295155</v>
       </c>
       <c r="B54" t="n">
-        <v>78882</v>
+        <v>79084</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5748,34 +5731,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>377249</v>
+        <v>377489</v>
       </c>
       <c r="R54" t="n">
-        <v>6744297</v>
+        <v>6744396</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5822,22 +5805,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128360475</v>
+        <v>128360453</v>
       </c>
       <c r="B55" t="n">
-        <v>78881</v>
+        <v>79084</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5869,10 +5852,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>377558</v>
+        <v>377483</v>
       </c>
       <c r="R55" t="n">
-        <v>6744145</v>
+        <v>6744504</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5931,10 +5914,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128360482</v>
+        <v>128360474</v>
       </c>
       <c r="B56" t="n">
-        <v>78882</v>
+        <v>79084</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5942,21 +5925,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5966,10 +5949,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>377306</v>
+        <v>377558</v>
       </c>
       <c r="R56" t="n">
-        <v>6744244</v>
+        <v>6744145</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6028,10 +6011,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128360460</v>
+        <v>128360487</v>
       </c>
       <c r="B57" t="n">
-        <v>79124</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6039,21 +6022,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6063,10 +6046,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>377453</v>
+        <v>377564</v>
       </c>
       <c r="R57" t="n">
-        <v>6744153</v>
+        <v>6744311</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6125,10 +6108,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128360476</v>
+        <v>127295099</v>
       </c>
       <c r="B58" t="n">
-        <v>78882</v>
+        <v>79946</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6136,34 +6119,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>377558</v>
+        <v>377505</v>
       </c>
       <c r="R58" t="n">
-        <v>6744145</v>
+        <v>6744534</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6210,22 +6193,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128360467</v>
+        <v>127295101</v>
       </c>
       <c r="B59" t="n">
-        <v>79124</v>
+        <v>79946</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6233,34 +6216,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>377532</v>
+        <v>377493</v>
       </c>
       <c r="R59" t="n">
-        <v>6744383</v>
+        <v>6744550</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6307,22 +6290,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128360449</v>
+        <v>127295109</v>
       </c>
       <c r="B60" t="n">
-        <v>78882</v>
+        <v>79946</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6330,34 +6313,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>377237</v>
+        <v>377479</v>
       </c>
       <c r="R60" t="n">
-        <v>6744295</v>
+        <v>6744536</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6404,22 +6387,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128360485</v>
+        <v>127295114</v>
       </c>
       <c r="B61" t="n">
-        <v>79124</v>
+        <v>79946</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6427,34 +6410,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>377332</v>
+        <v>377455</v>
       </c>
       <c r="R61" t="n">
-        <v>6744250</v>
+        <v>6744199</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6501,22 +6484,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128360464</v>
+        <v>127295115</v>
       </c>
       <c r="B62" t="n">
-        <v>79124</v>
+        <v>79946</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6524,34 +6507,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>377405</v>
+        <v>377494</v>
       </c>
       <c r="R62" t="n">
-        <v>6744360</v>
+        <v>6744143</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6598,22 +6581,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128360465</v>
+        <v>127295119</v>
       </c>
       <c r="B63" t="n">
-        <v>79156</v>
+        <v>79946</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6621,34 +6604,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>377505</v>
+        <v>377599</v>
       </c>
       <c r="R63" t="n">
-        <v>6744610</v>
+        <v>6744109</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6695,22 +6678,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128360450</v>
+        <v>127295121</v>
       </c>
       <c r="B64" t="n">
-        <v>79156</v>
+        <v>79946</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6718,34 +6701,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>377189</v>
+        <v>377523</v>
       </c>
       <c r="R64" t="n">
-        <v>6744221</v>
+        <v>6744136</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6792,22 +6775,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128360447</v>
+        <v>127295147</v>
       </c>
       <c r="B65" t="n">
-        <v>79743</v>
+        <v>79946</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6835,14 +6818,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q65" t="n">
         <v>377575</v>
       </c>
       <c r="R65" t="n">
-        <v>6744372</v>
+        <v>6744364</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6889,22 +6872,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128360463</v>
+        <v>127295150</v>
       </c>
       <c r="B66" t="n">
-        <v>79124</v>
+        <v>79946</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6912,34 +6895,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>377620</v>
+        <v>377507</v>
       </c>
       <c r="R66" t="n">
-        <v>6744362</v>
+        <v>6744400</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -6986,22 +6969,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128360487</v>
+        <v>127295167</v>
       </c>
       <c r="B67" t="n">
-        <v>78881</v>
+        <v>79946</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7009,34 +6992,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>377564</v>
+        <v>377647</v>
       </c>
       <c r="R67" t="n">
-        <v>6744311</v>
+        <v>6744358</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7077,28 +7060,29 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128360445</v>
+        <v>128360447</v>
       </c>
       <c r="B68" t="n">
-        <v>79124</v>
+        <v>79946</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7106,21 +7090,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7130,10 +7114,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>377247</v>
+        <v>377575</v>
       </c>
       <c r="R68" t="n">
-        <v>6744296</v>
+        <v>6744372</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7192,10 +7176,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128360488</v>
+        <v>127295104</v>
       </c>
       <c r="B69" t="n">
-        <v>78882</v>
+        <v>79085</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7223,14 +7207,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>377564</v>
+        <v>377491</v>
       </c>
       <c r="R69" t="n">
-        <v>6744311</v>
+        <v>6744551</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7277,22 +7261,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128360470</v>
+        <v>127295105</v>
       </c>
       <c r="B70" t="n">
-        <v>79124</v>
+        <v>79085</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7300,34 +7284,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>377452</v>
+        <v>377468</v>
       </c>
       <c r="R70" t="n">
-        <v>6744550</v>
+        <v>6744527</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7374,22 +7358,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128360453</v>
+        <v>127295106</v>
       </c>
       <c r="B71" t="n">
-        <v>78881</v>
+        <v>79085</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7397,34 +7381,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>377483</v>
+        <v>377535</v>
       </c>
       <c r="R71" t="n">
-        <v>6744504</v>
+        <v>6744318</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7471,22 +7455,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Dick Östberg</t>
+          <t>Helena Malmestrand</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128360454</v>
+        <v>127295107</v>
       </c>
       <c r="B72" t="n">
-        <v>78882</v>
+        <v>79085</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7514,14 +7498,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Hedtjärnsberget, Vrm</t>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>377483</v>
+        <v>377557</v>
       </c>
       <c r="R72" t="n">
-        <v>6744504</v>
+        <v>6744301</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7568,15 +7552,1374 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>127295108</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>377545</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6744314</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>127295113</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>377452</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6744197</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>127295118</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>377523</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6744132</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>127295129</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>377236</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6744248</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>127295154</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>377487</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6744422</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>127295156</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>377489</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6744396</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127295161</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>377576</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6744414</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>128360449</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>377237</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6744295</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
           <t>Dick Östberg</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
+      <c r="AX80" t="inlineStr">
         <is>
           <t>Dick Östberg</t>
         </is>
       </c>
-      <c r="AY72" t="inlineStr"/>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>128360454</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>377483</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6744504</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>128360476</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>377558</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6744145</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>128360480</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>377249</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6744297</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>128360482</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>377306</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6744244</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>128360488</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Hedtjärnsberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>377564</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6744311</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Dick Östberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127295116</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Djupbäckmyren, Hedtjärnberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>377494</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6744143</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Norra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-06-18</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 22621-2025 artfynd.xlsx
+++ b/artfynd/A 22621-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY86"/>
+  <dimension ref="A1:AZ86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295126</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110083903</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295127</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295128</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295138</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295148</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295157</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295164</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360450</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360456</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360465</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360481</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295143</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295162</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295139</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74111086</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295149</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110083906</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295102</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295103</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295111</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295117</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295130</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295131</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295132</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3194,6 +3324,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295133</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3291,6 +3426,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295135</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3388,6 +3528,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295136</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3485,6 +3630,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295140</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3582,6 +3732,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295142</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3679,6 +3834,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295144</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3776,6 +3936,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295145</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3873,6 +4038,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295146</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3970,6 +4140,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295151</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4067,6 +4242,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295158</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4164,6 +4344,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295160</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4261,6 +4446,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295163</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4358,6 +4548,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295165</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4455,6 +4650,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360445</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4552,6 +4752,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360460</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4649,6 +4854,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360463</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4746,6 +4956,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360464</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4843,6 +5058,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360467</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4940,6 +5160,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360469</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5037,6 +5262,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360470</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5134,6 +5364,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360478</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5231,6 +5466,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360485</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5328,6 +5568,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360489</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5425,6 +5670,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295134</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5522,6 +5772,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295100</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5619,6 +5874,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295112</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5717,6 +5977,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295152</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5814,6 +6079,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295155</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5911,6 +6181,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360453</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6008,6 +6283,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360474</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6105,6 +6385,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360487</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6202,6 +6487,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295099</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6299,6 +6589,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295101</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6396,6 +6691,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295109</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6493,6 +6793,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295114</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6590,6 +6895,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295115</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6687,6 +6997,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295119</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6784,6 +7099,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295121</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6881,6 +7201,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295147</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -6978,6 +7303,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295150</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7076,6 +7406,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295167</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7173,6 +7508,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360447</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7270,6 +7610,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295104</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7367,6 +7712,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295105</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7464,6 +7814,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295106</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7561,6 +7916,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295107</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7658,6 +8018,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295108</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7755,6 +8120,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295113</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7852,6 +8222,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295118</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -7949,6 +8324,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295129</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8047,6 +8427,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295154</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8144,6 +8529,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295156</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8241,6 +8631,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295161</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8338,6 +8733,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360449</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8435,6 +8835,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360454</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8532,6 +8937,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360476</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8629,6 +9039,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360480</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8726,6 +9141,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360482</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8823,6 +9243,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128360488</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8920,8 +9345,100 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127295116</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>